--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CC2993-0FC8-4805-85F3-A2488E346C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9C981B-4291-4C74-A70A-21458F5927DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,16 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId3"/>
     <sheet name="画面遷移図" sheetId="3" state="hidden" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="クラス" sheetId="8" r:id="rId6"/>
+    <sheet name="クラス" sheetId="8" state="hidden" r:id="rId6"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" state="hidden" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="158">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -387,10 +387,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクテーブルにアクセスするDAOクラス</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ConnectionManager.java</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -662,6 +658,110 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>JudgeUserServlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>POST</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>①</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>submit</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>delete</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>②</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>edit</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザ認証をし、真の場合削除画面へ画像遷移する。</t>
+    <rPh sb="3" eb="5">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザ認証をし、真の場合編集画面へ画像遷移する。</t>
+    <rPh sb="12" eb="14">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タスクテーブルにアクセスする</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DAO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>クラス</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -670,7 +770,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -682,6 +782,8 @@
       <sz val="26"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -693,26 +795,36 @@
       <sz val="28"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
@@ -752,6 +864,21 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1721,7 +1848,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1866,6 +1993,42 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1893,12 +2056,111 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1908,120 +2170,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2040,78 +2209,54 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2121,23 +2266,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2161,22 +2294,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>83546</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1070785</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>23435</xdr:rowOff>
+      <xdr:colOff>1118101</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>118139</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA0580B4-346B-E5C8-F842-3BCF1FB23202}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F156B090-F720-D488-4B07-F035C9520272}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2192,14 +2325,263 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="83546" y="896471"/>
-          <a:ext cx="9092827" cy="4555591"/>
+          <a:off x="0" y="886047"/>
+          <a:ext cx="9181124" cy="4504069"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>337710</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66252</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>590912</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>64161</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3563CDE2-01D1-2D63-42A3-AF1E2C647B96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1393493" y="1611674"/>
+          <a:ext cx="6105913" cy="1604535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>722281</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>74530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1154281</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>48073</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32B84C00-AB18-CFBB-B898-FC2BB9C26340}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6460233" y="2691036"/>
+          <a:ext cx="432000" cy="509085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1162892</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>76507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>424350</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>50050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4FE5EDD-ED39-4D68-9A8B-4B9CC2B935F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6900844" y="2693013"/>
+          <a:ext cx="432000" cy="509085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>750455</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19242</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>663864</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>14431</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B754F75D-4664-052D-9D07-C11BB6F3D1D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6494319" y="3155757"/>
+          <a:ext cx="1082386" cy="485871"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>①　　②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2412,85 +2794,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2510,48 +2892,48 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="48" t="s">
+      <c r="H13" s="62"/>
+      <c r="I13" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="48"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="56">
+      <c r="G14" s="60"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="68">
         <v>45705</v>
       </c>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="48"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2560,13 +2942,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="51" t="s">
+      <c r="G17" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3580,19 +3962,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="91"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -3604,192 +3986,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="65">
+      <c r="E2" s="105"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="108">
         <v>45705</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="101"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="92" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="93"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="74"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="74" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="75"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="76"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="74" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="75"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="76"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="74" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="75"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="76"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="75"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="77" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="76"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="72" t="s">
+      <c r="A10" s="94"/>
+      <c r="B10" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="75"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="76"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="89"/>
-      <c r="B11" s="72" t="s">
+      <c r="A11" s="95"/>
+      <c r="B11" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="48" t="s">
+      <c r="C11" s="62"/>
+      <c r="D11" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="74" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="75"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="76"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="90" t="s">
+      <c r="B13" s="70"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="91"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="71"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4780,6 +5162,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4788,25 +5189,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4825,19 +5207,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="91"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -4849,46 +5231,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="65">
+      <c r="A2" s="85"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="104" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="105"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="108">
         <v>45706</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="101"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6236,19 +6618,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="91"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6260,40 +6642,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="69"/>
+      <c r="A2" s="85"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="101"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7652,19 +8034,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="91"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7676,197 +8058,201 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="104" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="105"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="108">
+        <v>45706</v>
+      </c>
+      <c r="I2" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="100"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="85"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="101"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="85"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="101"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="111" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="114" t="s">
         <v>145</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="65">
-        <v>45706</v>
-      </c>
-      <c r="I2" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="69"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="70"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="70"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="106" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="100" t="s">
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="74"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="76"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="85"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="118"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="85"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="118"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="85"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="118"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="85"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="118"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="85"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="118"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="85"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="118"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="76"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="93"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="98" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="75"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="101"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="82"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="104"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="82"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="104"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="82"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="104"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="82"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="104"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="82"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="104"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="82"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="104"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="98" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="75"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="98" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="16"/>
+      <c r="J15" s="16" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -7879,95 +8265,119 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="105" t="s">
+      <c r="H16" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="75"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="76"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="99"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="75"/>
+      <c r="A17" s="110" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H17" s="75" t="s">
+        <v>155</v>
+      </c>
+      <c r="I17" s="61"/>
+      <c r="J17" s="76"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="75"/>
+      <c r="A18" s="110" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="I18" s="61"/>
+      <c r="J18" s="76"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="99"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="62"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="76"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="99"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="76"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="99"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
+      <c r="A21" s="110"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="76"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="99"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
+      <c r="A22" s="110"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="76"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="107"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
+      <c r="A23" s="112"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="81"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="91"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8948,17 +9358,10 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
@@ -8975,14 +9378,22 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9011,7 +9422,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="120" t="s">
         <v>80</v>
       </c>
       <c r="B2" s="39" t="s">
@@ -9020,58 +9431,58 @@
       <c r="C2" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="139" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="109" t="s">
+      <c r="A3" s="120"/>
+      <c r="B3" s="121" t="s">
         <v>83</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="140" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19.5" customHeight="1">
+      <c r="A4" s="120"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="39" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A4" s="108"/>
-      <c r="B4" s="109"/>
-      <c r="C4" s="39" t="s">
+      <c r="D4" s="39" t="s">
         <v>87</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.5" customHeight="1">
       <c r="A5" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="C5" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="D5" s="38" t="s">
         <v>91</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.5" customHeight="1">
       <c r="A6" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="C6" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="D6" s="38" t="s">
         <v>95</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -9081,6 +9492,7 @@
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9095,182 +9507,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="57" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="57" t="s">
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="57" t="s">
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="57" t="s">
+      <c r="P1" s="91"/>
+      <c r="Q1" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="58"/>
-      <c r="S1" s="57" t="s">
+      <c r="R1" s="91"/>
+      <c r="S1" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="93"/>
+      <c r="T1" s="74"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="103"/>
+      <c r="A2" s="85"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="117"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="104"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="106"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="106"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="106"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="114"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="107"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="107"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="107"/>
+      <c r="T4" s="130"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="92" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="93"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="74"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="74" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="75"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="76"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="74" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="75"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="76"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9469,37 +9881,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="117" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="105" t="s">
+      <c r="D15" s="62"/>
+      <c r="E15" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="105" t="s">
+      <c r="F15" s="62"/>
+      <c r="G15" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="105" t="s">
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="105" t="s">
+      <c r="K15" s="62"/>
+      <c r="L15" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="49"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="105" t="s">
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="50"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="62"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -9511,37 +9923,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="115">
+      <c r="A16" s="122">
         <v>1</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="116" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="116" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="110" t="s">
+      <c r="F16" s="62"/>
+      <c r="G16" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="110" t="s">
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="50"/>
-      <c r="L16" s="112" t="s">
+      <c r="K16" s="62"/>
+      <c r="L16" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="49"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="112" t="s">
+      <c r="M16" s="61"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="50"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="62"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -9553,37 +9965,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="115">
+      <c r="A17" s="122">
         <v>2</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="116" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="116" t="s">
+      <c r="D17" s="62"/>
+      <c r="E17" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="110" t="s">
+      <c r="F17" s="62"/>
+      <c r="G17" s="128" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="110" t="s">
+      <c r="H17" s="61"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="50"/>
-      <c r="L17" s="112" t="s">
+      <c r="K17" s="62"/>
+      <c r="L17" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="112" t="s">
+      <c r="M17" s="61"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="50"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="62"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -9595,23 +10007,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="50"/>
+      <c r="A18" s="122"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="62"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -9623,23 +10035,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="115"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="50"/>
+      <c r="A19" s="122"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="62"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -9651,23 +10063,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="115"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="50"/>
+      <c r="A20" s="122"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="126"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="62"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -9679,23 +10091,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="115"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="112"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="50"/>
+      <c r="A21" s="122"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="126"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="62"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -9707,23 +10119,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="115"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="50"/>
+      <c r="A22" s="122"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="126"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="126"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="62"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -9735,23 +10147,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="115"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="116"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="50"/>
+      <c r="A23" s="122"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="126"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="62"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -9763,23 +10175,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="115"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="116"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="112"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="50"/>
+      <c r="A24" s="122"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="62"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -9791,23 +10203,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="115"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="50"/>
+      <c r="A25" s="122"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="62"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -9819,23 +10231,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="115"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="50"/>
+      <c r="A26" s="122"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="128"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="126"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="126"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="62"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -9847,23 +10259,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="115"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="50"/>
+      <c r="A27" s="122"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="126"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="126"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="62"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -9875,23 +10287,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="115"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="50"/>
+      <c r="A28" s="122"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="128"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="126"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="126"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="62"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -9903,23 +10315,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="115"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
+      <c r="A29" s="122"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="126"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="126"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="62"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -9931,23 +10343,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="115"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="116"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
+      <c r="A30" s="122"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="126"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="126"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="62"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -9959,23 +10371,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="118"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="78"/>
+      <c r="A31" s="124"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="125"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="127"/>
+      <c r="P31" s="70"/>
+      <c r="Q31" s="81"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10973,6 +11385,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10997,118 +11521,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11131,61 +11543,61 @@
   <sheetData>
     <row r="1" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="2" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F2" s="130" t="s">
-        <v>138</v>
-      </c>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134" t="s">
+      <c r="F2" s="136" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="54"/>
+      <c r="I2" s="55" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="6:9" ht="13" customHeight="1" thickBot="1">
+      <c r="F3" s="137"/>
+      <c r="H3" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="6:9" ht="13" customHeight="1" thickBot="1">
+      <c r="F4" s="138"/>
+      <c r="H4" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="I4" s="59" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F3" s="131"/>
-      <c r="H3" s="135" t="s">
-        <v>136</v>
-      </c>
-      <c r="I3" s="136" t="s">
+    <row r="5" spans="6:9" ht="13" customHeight="1" thickBot="1">
+      <c r="H5" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="I5" s="59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="6:9" ht="13" customHeight="1" thickBot="1">
+      <c r="H6" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="57" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F4" s="132"/>
-      <c r="H4" s="137" t="s">
-        <v>136</v>
-      </c>
-      <c r="I4" s="138" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H5" s="137" t="s">
-        <v>136</v>
-      </c>
-      <c r="I5" s="138" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H6" s="135" t="s">
-        <v>136</v>
-      </c>
-      <c r="I6" s="136" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="8" spans="6:9" ht="13" customHeight="1">
-      <c r="H8" s="120" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="121"/>
+      <c r="H8" s="132" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="133"/>
     </row>
     <row r="9" spans="6:9" ht="13" customHeight="1">
       <c r="H9" s="40" t="s">
         <v>73</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="6:9" ht="13" customHeight="1">
@@ -11193,7 +11605,7 @@
         <v>73</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="6:9" ht="13" customHeight="1">
@@ -11201,7 +11613,7 @@
         <v>73</v>
       </c>
       <c r="I11" s="43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="6:9" ht="13" customHeight="1">
@@ -11209,7 +11621,7 @@
         <v>73</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="6:9" ht="13" customHeight="1">
@@ -11217,7 +11629,7 @@
         <v>73</v>
       </c>
       <c r="I13" s="43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="6:9" ht="13" customHeight="1">
@@ -11225,7 +11637,7 @@
         <v>73</v>
       </c>
       <c r="I14" s="43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="6:9" ht="13" customHeight="1">
@@ -11233,7 +11645,7 @@
         <v>73</v>
       </c>
       <c r="I15" s="43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="6:9" ht="13" customHeight="1">
@@ -11241,7 +11653,7 @@
         <v>73</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="8:9" ht="13" customHeight="1">
@@ -11249,225 +11661,225 @@
         <v>73</v>
       </c>
       <c r="I17" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="8:9" ht="13" customHeight="1">
       <c r="H18" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="41" t="s">
         <v>107</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="19" spans="8:9" ht="13" customHeight="1">
       <c r="H19" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I19" s="43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="8:9" ht="13" customHeight="1">
       <c r="H20" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I20" s="43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="8:9" ht="13" customHeight="1">
       <c r="H21" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I21" s="43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="8:9" ht="13" customHeight="1">
       <c r="H22" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I22" s="43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="8:9" ht="13" customHeight="1">
       <c r="H23" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I23" s="43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="8:9" ht="13" customHeight="1">
       <c r="H24" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I24" s="43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="8:9" ht="13" customHeight="1">
       <c r="H25" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I25" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="8:9" ht="13" customHeight="1">
       <c r="H26" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I26" s="43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="8:9" ht="13" customHeight="1">
       <c r="H27" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I27" s="43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="8:9" ht="13" customHeight="1">
       <c r="H28" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I28" s="43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="8:9" ht="13" customHeight="1">
       <c r="H29" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I29" s="43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="8:9" ht="13" customHeight="1">
       <c r="H30" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I30" s="43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="8:9" ht="13" customHeight="1">
       <c r="H31" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I31" s="43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="8:9" ht="13" customHeight="1">
       <c r="H32" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I32" s="43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="13" customHeight="1">
       <c r="H33" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I33" s="43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="13" customHeight="1">
       <c r="H34" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I34" s="43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="13" customHeight="1">
       <c r="H35" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I35" s="43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H36" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I36" s="47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="38" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H38" s="126" t="s">
+      <c r="H38" s="134" t="s">
+        <v>130</v>
+      </c>
+      <c r="I38" s="135"/>
+    </row>
+    <row r="39" spans="2:9" ht="13" customHeight="1" thickBot="1">
+      <c r="H39" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="I38" s="127"/>
-    </row>
-    <row r="39" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H39" s="122" t="s">
+      <c r="I39" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="I39" s="123" t="s">
+    </row>
+    <row r="40" spans="2:9" ht="13" customHeight="1" thickBot="1">
+      <c r="H40" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="I40" s="49" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H40" s="122" t="s">
-        <v>132</v>
-      </c>
-      <c r="I40" s="123" t="s">
+    <row r="41" spans="2:9" ht="13" customHeight="1" thickBot="1">
+      <c r="H41" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="I41" s="51" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H41" s="124" t="s">
-        <v>132</v>
-      </c>
-      <c r="I41" s="125" t="s">
+    <row r="42" spans="2:9" ht="13" customHeight="1" thickBot="1">
+      <c r="H42" s="50" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="42" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H42" s="124" t="s">
+      <c r="I42" s="51" t="s">
         <v>136</v>
-      </c>
-      <c r="I42" s="125" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="44" spans="2:9" ht="13" customHeight="1">
-      <c r="B44" s="120" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="121"/>
+      <c r="B44" s="132" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="133"/>
     </row>
     <row r="45" spans="2:9" ht="2" customHeight="1">
-      <c r="B45" s="128"/>
-      <c r="C45" s="129"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="53"/>
     </row>
     <row r="46" spans="2:9" ht="13" customHeight="1">
       <c r="B46" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C46" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="B47" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9C981B-4291-4C74-A70A-21458F5927DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE927B3-4198-4D0F-B166-76B7D4F7598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId3"/>
-    <sheet name="画面遷移図" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="画面遷移図" sheetId="3" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="クラス" sheetId="8" state="hidden" r:id="rId6"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="158">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -2339,6 +2339,61 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>588655</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>48105</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E34253F-1D6E-2DFB-EFB6-F03CEBC40EDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="923636"/>
+          <a:ext cx="6313276" cy="4791363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -6645,12 +6700,18 @@
       <c r="A2" s="85"/>
       <c r="B2" s="64"/>
       <c r="C2" s="86"/>
-      <c r="D2" s="104"/>
+      <c r="D2" s="104" t="s">
+        <v>144</v>
+      </c>
       <c r="E2" s="105"/>
       <c r="F2" s="104"/>
       <c r="G2" s="105"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
+      <c r="H2" s="108">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="97" t="s">
+        <v>70</v>
+      </c>
       <c r="J2" s="100"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
@@ -8017,6 +8078,7 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE927B3-4198-4D0F-B166-76B7D4F7598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106FFB44-948A-4601-9CC3-E668391A7CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="159">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -659,10 +659,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>JudgeUserServlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>POST</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -723,13 +719,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザ認証をし、真の場合編集画面へ画像遷移する。</t>
-    <rPh sb="12" eb="14">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -760,6 +749,39 @@
       </rPr>
       <t>クラス</t>
     </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>JudgeUserDeleteServlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>JudgeUserEditServlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザ認証をし、真の場合編集画面へ画像遷移する。</t>
+    <rPh sb="3" eb="5">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センイ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1848,7 +1870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2029,6 +2051,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2056,31 +2084,118 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2089,108 +2204,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2215,36 +2243,36 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2266,11 +2294,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2639,6 +2676,74 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>750455</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19242</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>663864</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>14431</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="テキスト ボックス 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEA2233E-6546-4F02-945F-88978944B008}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6503253" y="3141325"/>
+          <a:ext cx="1085135" cy="494118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>　</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2849,85 +2954,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2947,48 +3052,48 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="62"/>
-      <c r="I13" s="60" t="s">
+      <c r="H13" s="64"/>
+      <c r="I13" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="64"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="60"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="68">
+      <c r="G14" s="62"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="70">
         <v>45705</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="62"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="64"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="60"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2997,13 +3102,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="63" t="s">
+      <c r="G17" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="66"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4017,19 +4122,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="91"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="91"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -4041,192 +4146,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="96"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
         <v>45705</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="100"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="85"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="72" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="74"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="75" t="s">
+      <c r="B6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="76"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="75" t="s">
+      <c r="B7" s="63"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="76"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="75" t="s">
+      <c r="B8" s="63"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="76"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="77" t="s">
+      <c r="C9" s="64"/>
+      <c r="D9" s="108" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="76"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="89"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="96" t="s">
+      <c r="A10" s="102"/>
+      <c r="B10" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="77" t="s">
+      <c r="C10" s="64"/>
+      <c r="D10" s="108" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="76"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96" t="s">
+      <c r="A11" s="103"/>
+      <c r="B11" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="60" t="s">
+      <c r="C11" s="64"/>
+      <c r="D11" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="79"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="110"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="75" t="s">
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="76"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="89"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="80" t="s">
+      <c r="A13" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="70"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="69" t="s">
+      <c r="B13" s="91"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="71"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5217,17 +5322,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5236,14 +5338,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5262,19 +5367,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="91"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="91"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5286,46 +5391,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="96"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
         <v>45706</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="100"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="85"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6673,19 +6778,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="91"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="91"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6697,46 +6802,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="96"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
         <v>45707</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="100"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="85"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8096,19 +8201,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="103" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="91"/>
-      <c r="F1" s="103" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="91"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8120,201 +8225,201 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="104" t="s">
+      <c r="A2" s="96"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="108">
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
         <v>45706</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="100"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="85"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="101"/>
+      <c r="A4" s="96"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="84"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="114" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="74"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="76"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="85"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="118"/>
+      <c r="A8" s="96"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="85"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="118"/>
+      <c r="A9" s="96"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="85"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="118"/>
+      <c r="A10" s="96"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="85"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="118"/>
+      <c r="A11" s="96"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="85"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="118"/>
+      <c r="A12" s="96"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="85"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="118"/>
+      <c r="A13" s="96"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="113" t="s">
+      <c r="A14" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="76"/>
+      <c r="B14" s="143"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="145"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="75" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
+      <c r="B15" s="143"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="88" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="142"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="113" t="s">
+      <c r="A16" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -8327,119 +8432,129 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="119" t="s">
+      <c r="H16" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="61"/>
-      <c r="J16" s="76"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="89"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="110" t="s">
-        <v>148</v>
-      </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="62"/>
+      <c r="A17" s="115" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="64"/>
       <c r="D17" s="17" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="H17" s="88" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="63"/>
+      <c r="J17" s="89"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="143"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
+      <c r="I18" s="143"/>
+      <c r="J18" s="145"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="143"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="88" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="141"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="H17" s="75" t="s">
-        <v>155</v>
-      </c>
-      <c r="I17" s="61"/>
-      <c r="J17" s="76"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="110" t="s">
+      <c r="B20" s="63"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="18" t="s">
+      <c r="G20" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G18" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="H18" s="75" t="s">
-        <v>156</v>
-      </c>
-      <c r="I18" s="61"/>
-      <c r="J18" s="76"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="76"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="76"/>
+      <c r="H20" s="88" t="s">
+        <v>158</v>
+      </c>
+      <c r="I20" s="63"/>
+      <c r="J20" s="89"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="62"/>
+      <c r="A21" s="115"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="64"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="76"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="110"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="62"/>
+      <c r="A22" s="115"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="64"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="76"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="112"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="81"/>
+      <c r="A23" s="113"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="71"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="105"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9419,12 +9534,16 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+  <mergeCells count="30">
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9441,16 +9560,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9484,7 +9598,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="122" t="s">
         <v>80</v>
       </c>
       <c r="B2" s="39" t="s">
@@ -9493,25 +9607,25 @@
       <c r="C2" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="60" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="121" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123" t="s">
         <v>83</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="140" t="s">
-        <v>157</v>
+      <c r="D3" s="61" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A4" s="120"/>
-      <c r="B4" s="121"/>
+      <c r="A4" s="122"/>
+      <c r="B4" s="123"/>
       <c r="C4" s="39" t="s">
         <v>86</v>
       </c>
@@ -9569,182 +9683,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="103" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="103" t="s">
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="103" t="s">
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="103" t="s">
+      <c r="P1" s="72"/>
+      <c r="Q1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="91"/>
-      <c r="S1" s="103" t="s">
+      <c r="R1" s="72"/>
+      <c r="S1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="74"/>
+      <c r="T1" s="107"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="104"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="104"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="104"/>
-      <c r="T2" s="117"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="119"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="85"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="106"/>
-      <c r="T3" s="118"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="120"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="130"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="128"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="72" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="74"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="107"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="75" t="s">
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="76"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="63"/>
+      <c r="S6" s="63"/>
+      <c r="T6" s="89"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="75" t="s">
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="61"/>
-      <c r="S7" s="61"/>
-      <c r="T7" s="76"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="63"/>
+      <c r="T7" s="89"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9943,37 +10057,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="129" t="s">
+      <c r="B15" s="64"/>
+      <c r="C15" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="119" t="s">
+      <c r="D15" s="64"/>
+      <c r="E15" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="119" t="s">
+      <c r="F15" s="64"/>
+      <c r="G15" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="119" t="s">
+      <c r="H15" s="63"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="62"/>
-      <c r="L15" s="119" t="s">
+      <c r="K15" s="64"/>
+      <c r="L15" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="119" t="s">
+      <c r="M15" s="63"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="64"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -9985,37 +10099,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="122">
+      <c r="A16" s="129">
         <v>1</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="123" t="s">
+      <c r="B16" s="64"/>
+      <c r="C16" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="123" t="s">
+      <c r="D16" s="64"/>
+      <c r="E16" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="128" t="s">
+      <c r="F16" s="64"/>
+      <c r="G16" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="128" t="s">
+      <c r="H16" s="63"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="62"/>
+      <c r="K16" s="64"/>
       <c r="L16" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="61"/>
-      <c r="N16" s="62"/>
+      <c r="M16" s="63"/>
+      <c r="N16" s="64"/>
       <c r="O16" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
+      <c r="P16" s="63"/>
+      <c r="Q16" s="64"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -10027,37 +10141,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="122">
+      <c r="A17" s="129">
         <v>2</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="123" t="s">
+      <c r="B17" s="64"/>
+      <c r="C17" s="130" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="123" t="s">
+      <c r="D17" s="64"/>
+      <c r="E17" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="128" t="s">
+      <c r="F17" s="64"/>
+      <c r="G17" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="128" t="s">
+      <c r="H17" s="63"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="62"/>
+      <c r="K17" s="64"/>
       <c r="L17" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="61"/>
-      <c r="N17" s="62"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="64"/>
       <c r="O17" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="62"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="64"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -10069,23 +10183,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="122"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="123"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="123"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="128"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="62"/>
+      <c r="A18" s="129"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="64"/>
       <c r="L18" s="126"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="64"/>
       <c r="O18" s="126"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="62"/>
+      <c r="P18" s="63"/>
+      <c r="Q18" s="64"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -10097,23 +10211,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="122"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="62"/>
+      <c r="A19" s="129"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="124"/>
+      <c r="K19" s="64"/>
       <c r="L19" s="126"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="62"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="64"/>
       <c r="O19" s="126"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="62"/>
+      <c r="P19" s="63"/>
+      <c r="Q19" s="64"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -10125,23 +10239,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="122"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="123"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="123"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="62"/>
+      <c r="A20" s="129"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="64"/>
       <c r="L20" s="126"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="62"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="64"/>
       <c r="O20" s="126"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="62"/>
+      <c r="P20" s="63"/>
+      <c r="Q20" s="64"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -10153,23 +10267,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="122"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="62"/>
+      <c r="A21" s="129"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="64"/>
       <c r="L21" s="126"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="62"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="64"/>
       <c r="O21" s="126"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="62"/>
+      <c r="P21" s="63"/>
+      <c r="Q21" s="64"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -10181,23 +10295,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="122"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="123"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="128"/>
-      <c r="K22" s="62"/>
+      <c r="A22" s="129"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="130"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="124"/>
+      <c r="K22" s="64"/>
       <c r="L22" s="126"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="64"/>
       <c r="O22" s="126"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="62"/>
+      <c r="P22" s="63"/>
+      <c r="Q22" s="64"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -10209,23 +10323,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="122"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="123"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="62"/>
+      <c r="A23" s="129"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="124"/>
+      <c r="K23" s="64"/>
       <c r="L23" s="126"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
       <c r="O23" s="126"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="62"/>
+      <c r="P23" s="63"/>
+      <c r="Q23" s="64"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -10237,23 +10351,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="122"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="123"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="62"/>
+      <c r="A24" s="129"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="130"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="64"/>
       <c r="L24" s="126"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="62"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="64"/>
       <c r="O24" s="126"/>
-      <c r="P24" s="61"/>
-      <c r="Q24" s="62"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="64"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -10265,23 +10379,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="122"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="123"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="128"/>
-      <c r="K25" s="62"/>
+      <c r="A25" s="129"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="130"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="130"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="124"/>
+      <c r="K25" s="64"/>
       <c r="L25" s="126"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="62"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="64"/>
       <c r="O25" s="126"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="62"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="64"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -10293,23 +10407,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="122"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="123"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="123"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="128"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="128"/>
-      <c r="K26" s="62"/>
+      <c r="A26" s="129"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="130"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="124"/>
+      <c r="K26" s="64"/>
       <c r="L26" s="126"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
       <c r="O26" s="126"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="62"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="64"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -10321,23 +10435,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="122"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="128"/>
-      <c r="K27" s="62"/>
+      <c r="A27" s="129"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="130"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="124"/>
+      <c r="K27" s="64"/>
       <c r="L27" s="126"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
       <c r="O27" s="126"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="62"/>
+      <c r="P27" s="63"/>
+      <c r="Q27" s="64"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -10349,23 +10463,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="122"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="123"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="123"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="128"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="62"/>
+      <c r="A28" s="129"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="124"/>
+      <c r="K28" s="64"/>
       <c r="L28" s="126"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="62"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="64"/>
       <c r="O28" s="126"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="62"/>
+      <c r="P28" s="63"/>
+      <c r="Q28" s="64"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -10377,23 +10491,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="122"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="123"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="128"/>
-      <c r="K29" s="62"/>
+      <c r="A29" s="129"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="130"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="124"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="124"/>
+      <c r="K29" s="64"/>
       <c r="L29" s="126"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="62"/>
+      <c r="M29" s="63"/>
+      <c r="N29" s="64"/>
       <c r="O29" s="126"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="62"/>
+      <c r="P29" s="63"/>
+      <c r="Q29" s="64"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -10405,23 +10519,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="122"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="123"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="123"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="128"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="62"/>
+      <c r="A30" s="129"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="130"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="124"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="124"/>
+      <c r="K30" s="64"/>
       <c r="L30" s="126"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="62"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="64"/>
       <c r="O30" s="126"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="62"/>
+      <c r="P30" s="63"/>
+      <c r="Q30" s="64"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -10433,23 +10547,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="124"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="125"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="125"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="81"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="125"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="125"/>
+      <c r="K31" s="92"/>
       <c r="L31" s="127"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="81"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="92"/>
       <c r="O31" s="127"/>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="81"/>
+      <c r="P31" s="91"/>
+      <c r="Q31" s="92"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11447,62 +11561,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11527,62 +11641,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11605,7 +11719,7 @@
   <sheetData>
     <row r="1" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="2" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F2" s="136" t="s">
+      <c r="F2" s="138" t="s">
         <v>137</v>
       </c>
       <c r="H2" s="54"/>
@@ -11614,7 +11728,7 @@
       </c>
     </row>
     <row r="3" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F3" s="137"/>
+      <c r="F3" s="139"/>
       <c r="H3" s="56" t="s">
         <v>135</v>
       </c>
@@ -11623,7 +11737,7 @@
       </c>
     </row>
     <row r="4" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F4" s="138"/>
+      <c r="F4" s="140"/>
       <c r="H4" s="58" t="s">
         <v>135</v>
       </c>
@@ -11649,10 +11763,10 @@
     </row>
     <row r="7" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="8" spans="6:9" ht="13" customHeight="1">
-      <c r="H8" s="132" t="s">
+      <c r="H8" s="134" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="133"/>
+      <c r="I8" s="135"/>
     </row>
     <row r="9" spans="6:9" ht="13" customHeight="1">
       <c r="H9" s="40" t="s">
@@ -11880,10 +11994,10 @@
     </row>
     <row r="37" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="38" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H38" s="134" t="s">
+      <c r="H38" s="136" t="s">
         <v>130</v>
       </c>
-      <c r="I38" s="135"/>
+      <c r="I38" s="137"/>
     </row>
     <row r="39" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H39" s="48" t="s">
@@ -11919,10 +12033,10 @@
     </row>
     <row r="43" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="44" spans="2:9" ht="13" customHeight="1">
-      <c r="B44" s="132" t="s">
+      <c r="B44" s="134" t="s">
         <v>126</v>
       </c>
-      <c r="C44" s="133"/>
+      <c r="C44" s="135"/>
     </row>
     <row r="45" spans="2:9" ht="2" customHeight="1">
       <c r="B45" s="52"/>

--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106FFB44-948A-4601-9CC3-E668391A7CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513C5956-A2FF-4FF7-A8DD-F521160BEDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -585,15 +585,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.ユーザーはメニュー画面から「タスク一覧表示」ボタンを押下する。
-2.システムはタスク一覧表示画面へ画面遷移する。
-3.タスク一覧、その横に「タスク削除」及び「タスク編集」ボタンが表示される。
-4.ユーザは「タスク削除」または「タスク編集」ボタンを押下する。(Alt-4)
-5.システムはタスク登録画面またはタスク編集画面へ画面遷移する。
-				</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ConnectionManager</t>
   </si>
   <si>
@@ -781,6 +772,18 @@
     </rPh>
     <rPh sb="19" eb="21">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.ユーザーはメニュー画面から「タスク一覧表示」ボタンを押下する。
+2.システムはタスク一覧表示画面へ画面遷移する。
+3.タスク一覧、その横に「タスク削除」及び「タスク編集」ボタンが表示される。
+4.ユーザは「タスク削除」または「タスク編集」ボタンを押下する。(Alt-4)
+5.システムはタスク削除画面またはタスク編集画面へ画面遷移する。
+				</t>
+    <rPh sb="148" eb="150">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -4260,7 +4263,7 @@
       </c>
       <c r="C9" s="64"/>
       <c r="D9" s="108" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="E9" s="63"/>
       <c r="F9" s="63"/>
@@ -5395,7 +5398,7 @@
       <c r="B2" s="66"/>
       <c r="C2" s="76"/>
       <c r="D2" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" s="74"/>
       <c r="F2" s="73"/>
@@ -6806,7 +6809,7 @@
       <c r="B2" s="66"/>
       <c r="C2" s="76"/>
       <c r="D2" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" s="74"/>
       <c r="F2" s="73"/>
@@ -8229,7 +8232,7 @@
       <c r="B2" s="66"/>
       <c r="C2" s="76"/>
       <c r="D2" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" s="74"/>
       <c r="F2" s="73"/>
@@ -8273,7 +8276,7 @@
       <c r="B5" s="100"/>
       <c r="C5" s="72"/>
       <c r="D5" s="116" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="100"/>
       <c r="F5" s="100"/>
@@ -8401,7 +8404,7 @@
       <c r="B15" s="143"/>
       <c r="C15" s="144"/>
       <c r="D15" s="88" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15" s="141"/>
       <c r="F15" s="141"/>
@@ -8411,7 +8414,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -8440,7 +8443,7 @@
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="115" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B17" s="63"/>
       <c r="C17" s="64"/>
@@ -8448,16 +8451,16 @@
         <v>73</v>
       </c>
       <c r="E17" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>150</v>
-      </c>
       <c r="H17" s="88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I17" s="63"/>
       <c r="J17" s="89"/>
@@ -8483,7 +8486,7 @@
       <c r="B19" s="143"/>
       <c r="C19" s="144"/>
       <c r="D19" s="88" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E19" s="141"/>
       <c r="F19" s="141"/>
@@ -8493,12 +8496,12 @@
         <v>26</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="115" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
@@ -8506,16 +8509,16 @@
         <v>73</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F20" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>153</v>
-      </c>
       <c r="H20" s="88" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I20" s="63"/>
       <c r="J20" s="89"/>
@@ -9620,7 +9623,7 @@
         <v>85</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1">
@@ -11720,45 +11723,45 @@
     <row r="1" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="2" spans="6:9" ht="13" customHeight="1" thickBot="1">
       <c r="F2" s="138" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H2" s="54"/>
       <c r="I2" s="55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="6:9" ht="13" customHeight="1" thickBot="1">
       <c r="F3" s="139"/>
       <c r="H3" s="56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I3" s="57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="6:9" ht="13" customHeight="1" thickBot="1">
       <c r="F4" s="140"/>
       <c r="H4" s="58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I4" s="59" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="6:9" ht="13" customHeight="1" thickBot="1">
       <c r="H5" s="58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="6:9" ht="13" customHeight="1" thickBot="1">
       <c r="H6" s="56" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I6" s="57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
@@ -11995,40 +11998,40 @@
     <row r="37" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="38" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H38" s="136" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I38" s="137"/>
     </row>
     <row r="39" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H39" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" s="49" t="s">
         <v>131</v>
-      </c>
-      <c r="I39" s="49" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H40" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I40" s="49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H41" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H42" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="I42" s="51" t="s">
         <v>135</v>
-      </c>
-      <c r="I42" s="51" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
@@ -12055,7 +12058,7 @@
         <v>106</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513C5956-A2FF-4FF7-A8DD-F521160BEDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842AF685-1E9B-4662-A0AF-5C1A159A05EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="11840" yWindow="1920" windowWidth="4760" windowHeight="9990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>

--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842AF685-1E9B-4662-A0AF-5C1A159A05EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AED9A7F-69EB-4040-96B9-D865BB79BA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="11840" yWindow="1920" windowWidth="4760" windowHeight="9990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,27 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId3"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="クラス" sheetId="8" state="hidden" r:id="rId6"/>
+    <sheet name="クラス" sheetId="8" r:id="rId6"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="9" state="hidden" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="168">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -785,6 +796,42 @@
     <rPh sb="148" eb="150">
       <t>サクジョ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>UserBean</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>userId:String</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>password:String</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>userName:String</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>UserBean()</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>getPassword():String</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>setPassword(password:String):void</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>getUserName():String</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>setUserName(userName:String):void</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2087,12 +2134,111 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2102,126 +2248,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2246,36 +2308,36 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2295,21 +2357,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4125,19 +4172,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -4149,70 +4196,70 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45705</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="106" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="94" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="63"/>
       <c r="C6" s="64"/>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="77" t="s">
         <v>68</v>
       </c>
       <c r="E6" s="63"/>
@@ -4220,15 +4267,15 @@
       <c r="G6" s="63"/>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
-      <c r="J6" s="89"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="94" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="63"/>
       <c r="C7" s="64"/>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="77" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="63"/>
@@ -4236,15 +4283,15 @@
       <c r="G7" s="63"/>
       <c r="H7" s="63"/>
       <c r="I7" s="63"/>
-      <c r="J7" s="89"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="94" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="63"/>
       <c r="C8" s="64"/>
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="77" t="s">
         <v>75</v>
       </c>
       <c r="E8" s="63"/>
@@ -4252,17 +4299,17 @@
       <c r="G8" s="63"/>
       <c r="H8" s="63"/>
       <c r="I8" s="63"/>
-      <c r="J8" s="89"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="98" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="64"/>
-      <c r="D9" s="108" t="s">
+      <c r="D9" s="79" t="s">
         <v>158</v>
       </c>
       <c r="E9" s="63"/>
@@ -4270,15 +4317,15 @@
       <c r="G9" s="63"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
-      <c r="J9" s="89"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="102"/>
-      <c r="B10" s="86" t="s">
+      <c r="A10" s="96"/>
+      <c r="B10" s="98" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="64"/>
-      <c r="D10" s="108" t="s">
+      <c r="D10" s="79" t="s">
         <v>128</v>
       </c>
       <c r="E10" s="63"/>
@@ -4286,31 +4333,31 @@
       <c r="G10" s="63"/>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
-      <c r="J10" s="89"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="103"/>
-      <c r="B11" s="86" t="s">
+      <c r="A11" s="97"/>
+      <c r="B11" s="98" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="64"/>
       <c r="D11" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="110"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="81"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="94" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="77" t="s">
         <v>71</v>
       </c>
       <c r="E12" s="63"/>
@@ -4318,23 +4365,23 @@
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
-      <c r="J12" s="89"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="91"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="104" t="s">
+      <c r="B13" s="72"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="105"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5325,6 +5372,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5333,25 +5399,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5373,16 +5420,16 @@
       <c r="A1" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5394,46 +5441,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45706</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6784,16 +6831,16 @@
       <c r="A1" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6805,46 +6852,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45707</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8207,16 +8254,16 @@
       <c r="A1" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8228,65 +8275,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45706</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="96"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="66"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="84"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="103"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="116" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="121" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="114" t="s">
+      <c r="A6" s="112" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="63"/>
@@ -8297,22 +8344,22 @@
       <c r="G6" s="63"/>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
-      <c r="J6" s="89"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="122"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="96"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="66"/>
       <c r="C8" s="66"/>
       <c r="D8" s="66"/>
@@ -8321,10 +8368,10 @@
       <c r="G8" s="66"/>
       <c r="H8" s="66"/>
       <c r="I8" s="66"/>
-      <c r="J8" s="120"/>
+      <c r="J8" s="125"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="96"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
       <c r="D9" s="66"/>
@@ -8333,10 +8380,10 @@
       <c r="G9" s="66"/>
       <c r="H9" s="66"/>
       <c r="I9" s="66"/>
-      <c r="J9" s="120"/>
+      <c r="J9" s="125"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="96"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
       <c r="D10" s="66"/>
@@ -8345,10 +8392,10 @@
       <c r="G10" s="66"/>
       <c r="H10" s="66"/>
       <c r="I10" s="66"/>
-      <c r="J10" s="120"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="96"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
       <c r="D11" s="66"/>
@@ -8357,10 +8404,10 @@
       <c r="G11" s="66"/>
       <c r="H11" s="66"/>
       <c r="I11" s="66"/>
-      <c r="J11" s="120"/>
+      <c r="J11" s="125"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="96"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
       <c r="D12" s="66"/>
@@ -8369,10 +8416,10 @@
       <c r="G12" s="66"/>
       <c r="H12" s="66"/>
       <c r="I12" s="66"/>
-      <c r="J12" s="120"/>
+      <c r="J12" s="125"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="96"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -8381,35 +8428,35 @@
       <c r="G13" s="66"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
-      <c r="J13" s="120"/>
+      <c r="J13" s="125"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="114" t="s">
+      <c r="A14" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="143"/>
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="143"/>
-      <c r="F14" s="143"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="143"/>
-      <c r="J14" s="145"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="143"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="88" t="s">
+      <c r="B15" s="113"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="77" t="s">
         <v>155</v>
       </c>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="142"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="116"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -8418,7 +8465,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="114" t="s">
+      <c r="A16" s="112" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="63"/>
@@ -8435,14 +8482,14 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="121" t="s">
+      <c r="H16" s="126" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="63"/>
-      <c r="J16" s="89"/>
+      <c r="J16" s="78"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="118" t="s">
         <v>146</v>
       </c>
       <c r="B17" s="63"/>
@@ -8459,39 +8506,39 @@
       <c r="G17" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="H17" s="88" t="s">
+      <c r="H17" s="77" t="s">
         <v>153</v>
       </c>
       <c r="I17" s="63"/>
-      <c r="J17" s="89"/>
+      <c r="J17" s="78"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114" t="s">
+      <c r="A18" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="143"/>
-      <c r="C18" s="143"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="143"/>
-      <c r="I18" s="143"/>
-      <c r="J18" s="145"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114" t="s">
+      <c r="A19" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="143"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="88" t="s">
+      <c r="B19" s="113"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="E19" s="141"/>
-      <c r="F19" s="141"/>
-      <c r="G19" s="141"/>
-      <c r="H19" s="142"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="116"/>
       <c r="I19" s="15" t="s">
         <v>26</v>
       </c>
@@ -8500,7 +8547,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="115" t="s">
+      <c r="A20" s="118" t="s">
         <v>150</v>
       </c>
       <c r="B20" s="63"/>
@@ -8517,47 +8564,47 @@
       <c r="G20" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="H20" s="88" t="s">
+      <c r="H20" s="77" t="s">
         <v>157</v>
       </c>
       <c r="I20" s="63"/>
-      <c r="J20" s="89"/>
+      <c r="J20" s="78"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="115"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="63"/>
       <c r="C21" s="64"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="88"/>
+      <c r="H21" s="77"/>
       <c r="I21" s="63"/>
-      <c r="J21" s="89"/>
+      <c r="J21" s="78"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="115"/>
+      <c r="A22" s="118"/>
       <c r="B22" s="63"/>
       <c r="C22" s="64"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="88"/>
+      <c r="H22" s="77"/>
       <c r="I22" s="63"/>
-      <c r="J22" s="89"/>
+      <c r="J22" s="78"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="113"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="120"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="105"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="73"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9538,15 +9585,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9563,11 +9606,15 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9601,7 +9648,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="127" t="s">
         <v>80</v>
       </c>
       <c r="B2" s="39" t="s">
@@ -9615,8 +9662,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123" t="s">
+      <c r="A3" s="127"/>
+      <c r="B3" s="128" t="s">
         <v>83</v>
       </c>
       <c r="C3" s="39" t="s">
@@ -9627,8 +9674,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A4" s="122"/>
-      <c r="B4" s="123"/>
+      <c r="A4" s="127"/>
+      <c r="B4" s="128"/>
       <c r="C4" s="39" t="s">
         <v>86</v>
       </c>
@@ -9686,133 +9733,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="71" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="71" t="s">
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="71" t="s">
+      <c r="P1" s="93"/>
+      <c r="Q1" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="72"/>
-      <c r="S1" s="71" t="s">
+      <c r="R1" s="93"/>
+      <c r="S1" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="107"/>
+      <c r="T1" s="76"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
       <c r="D2" s="66"/>
       <c r="E2" s="66"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="119"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="124"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
       <c r="C3" s="66"/>
       <c r="D3" s="66"/>
       <c r="E3" s="66"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="75"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="108"/>
       <c r="H3" s="66"/>
       <c r="I3" s="66"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="75"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="108"/>
       <c r="L3" s="66"/>
       <c r="M3" s="66"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="120"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="125"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="128"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="91"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="137"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="106" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="107"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="76"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="114" t="s">
+      <c r="A6" s="112" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="63"/>
@@ -9820,7 +9867,7 @@
       <c r="D6" s="63"/>
       <c r="E6" s="63"/>
       <c r="F6" s="64"/>
-      <c r="G6" s="88" t="s">
+      <c r="G6" s="77" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="63"/>
@@ -9835,10 +9882,10 @@
       <c r="Q6" s="63"/>
       <c r="R6" s="63"/>
       <c r="S6" s="63"/>
-      <c r="T6" s="89"/>
+      <c r="T6" s="78"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="114" t="s">
+      <c r="A7" s="112" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="63"/>
@@ -9846,7 +9893,7 @@
       <c r="D7" s="63"/>
       <c r="E7" s="63"/>
       <c r="F7" s="64"/>
-      <c r="G7" s="88" t="s">
+      <c r="G7" s="77" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="63"/>
@@ -9861,7 +9908,7 @@
       <c r="Q7" s="63"/>
       <c r="R7" s="63"/>
       <c r="S7" s="63"/>
-      <c r="T7" s="89"/>
+      <c r="T7" s="78"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10060,33 +10107,33 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="112" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="64"/>
-      <c r="C15" s="131" t="s">
+      <c r="C15" s="136" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="64"/>
-      <c r="E15" s="121" t="s">
+      <c r="E15" s="126" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="64"/>
-      <c r="G15" s="121" t="s">
+      <c r="G15" s="126" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="63"/>
       <c r="I15" s="64"/>
-      <c r="J15" s="121" t="s">
+      <c r="J15" s="126" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="64"/>
-      <c r="L15" s="121" t="s">
+      <c r="L15" s="126" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="63"/>
       <c r="N15" s="64"/>
-      <c r="O15" s="121" t="s">
+      <c r="O15" s="126" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="63"/>
@@ -10114,21 +10161,21 @@
         <v>54</v>
       </c>
       <c r="F16" s="64"/>
-      <c r="G16" s="124" t="s">
+      <c r="G16" s="135" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="64"/>
-      <c r="J16" s="124" t="s">
+      <c r="J16" s="135" t="s">
         <v>56</v>
       </c>
       <c r="K16" s="64"/>
-      <c r="L16" s="126" t="s">
+      <c r="L16" s="133" t="s">
         <v>57</v>
       </c>
       <c r="M16" s="63"/>
       <c r="N16" s="64"/>
-      <c r="O16" s="126" t="s">
+      <c r="O16" s="133" t="s">
         <v>58</v>
       </c>
       <c r="P16" s="63"/>
@@ -10156,21 +10203,21 @@
         <v>60</v>
       </c>
       <c r="F17" s="64"/>
-      <c r="G17" s="124" t="s">
+      <c r="G17" s="135" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="63"/>
       <c r="I17" s="64"/>
-      <c r="J17" s="124" t="s">
+      <c r="J17" s="135" t="s">
         <v>62</v>
       </c>
       <c r="K17" s="64"/>
-      <c r="L17" s="126" t="s">
+      <c r="L17" s="133" t="s">
         <v>63</v>
       </c>
       <c r="M17" s="63"/>
       <c r="N17" s="64"/>
-      <c r="O17" s="126" t="s">
+      <c r="O17" s="133" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="63"/>
@@ -10192,15 +10239,15 @@
       <c r="D18" s="64"/>
       <c r="E18" s="130"/>
       <c r="F18" s="64"/>
-      <c r="G18" s="124"/>
+      <c r="G18" s="135"/>
       <c r="H18" s="63"/>
       <c r="I18" s="64"/>
-      <c r="J18" s="124"/>
+      <c r="J18" s="135"/>
       <c r="K18" s="64"/>
-      <c r="L18" s="126"/>
+      <c r="L18" s="133"/>
       <c r="M18" s="63"/>
       <c r="N18" s="64"/>
-      <c r="O18" s="126"/>
+      <c r="O18" s="133"/>
       <c r="P18" s="63"/>
       <c r="Q18" s="64"/>
       <c r="R18" s="33"/>
@@ -10220,15 +10267,15 @@
       <c r="D19" s="64"/>
       <c r="E19" s="130"/>
       <c r="F19" s="64"/>
-      <c r="G19" s="124"/>
+      <c r="G19" s="135"/>
       <c r="H19" s="63"/>
       <c r="I19" s="64"/>
-      <c r="J19" s="124"/>
+      <c r="J19" s="135"/>
       <c r="K19" s="64"/>
-      <c r="L19" s="126"/>
+      <c r="L19" s="133"/>
       <c r="M19" s="63"/>
       <c r="N19" s="64"/>
-      <c r="O19" s="126"/>
+      <c r="O19" s="133"/>
       <c r="P19" s="63"/>
       <c r="Q19" s="64"/>
       <c r="R19" s="33"/>
@@ -10248,15 +10295,15 @@
       <c r="D20" s="64"/>
       <c r="E20" s="130"/>
       <c r="F20" s="64"/>
-      <c r="G20" s="124"/>
+      <c r="G20" s="135"/>
       <c r="H20" s="63"/>
       <c r="I20" s="64"/>
-      <c r="J20" s="124"/>
+      <c r="J20" s="135"/>
       <c r="K20" s="64"/>
-      <c r="L20" s="126"/>
+      <c r="L20" s="133"/>
       <c r="M20" s="63"/>
       <c r="N20" s="64"/>
-      <c r="O20" s="126"/>
+      <c r="O20" s="133"/>
       <c r="P20" s="63"/>
       <c r="Q20" s="64"/>
       <c r="R20" s="33"/>
@@ -10276,15 +10323,15 @@
       <c r="D21" s="64"/>
       <c r="E21" s="130"/>
       <c r="F21" s="64"/>
-      <c r="G21" s="124"/>
+      <c r="G21" s="135"/>
       <c r="H21" s="63"/>
       <c r="I21" s="64"/>
-      <c r="J21" s="124"/>
+      <c r="J21" s="135"/>
       <c r="K21" s="64"/>
-      <c r="L21" s="126"/>
+      <c r="L21" s="133"/>
       <c r="M21" s="63"/>
       <c r="N21" s="64"/>
-      <c r="O21" s="126"/>
+      <c r="O21" s="133"/>
       <c r="P21" s="63"/>
       <c r="Q21" s="64"/>
       <c r="R21" s="33"/>
@@ -10304,15 +10351,15 @@
       <c r="D22" s="64"/>
       <c r="E22" s="130"/>
       <c r="F22" s="64"/>
-      <c r="G22" s="124"/>
+      <c r="G22" s="135"/>
       <c r="H22" s="63"/>
       <c r="I22" s="64"/>
-      <c r="J22" s="124"/>
+      <c r="J22" s="135"/>
       <c r="K22" s="64"/>
-      <c r="L22" s="126"/>
+      <c r="L22" s="133"/>
       <c r="M22" s="63"/>
       <c r="N22" s="64"/>
-      <c r="O22" s="126"/>
+      <c r="O22" s="133"/>
       <c r="P22" s="63"/>
       <c r="Q22" s="64"/>
       <c r="R22" s="33"/>
@@ -10332,15 +10379,15 @@
       <c r="D23" s="64"/>
       <c r="E23" s="130"/>
       <c r="F23" s="64"/>
-      <c r="G23" s="124"/>
+      <c r="G23" s="135"/>
       <c r="H23" s="63"/>
       <c r="I23" s="64"/>
-      <c r="J23" s="124"/>
+      <c r="J23" s="135"/>
       <c r="K23" s="64"/>
-      <c r="L23" s="126"/>
+      <c r="L23" s="133"/>
       <c r="M23" s="63"/>
       <c r="N23" s="64"/>
-      <c r="O23" s="126"/>
+      <c r="O23" s="133"/>
       <c r="P23" s="63"/>
       <c r="Q23" s="64"/>
       <c r="R23" s="33"/>
@@ -10360,15 +10407,15 @@
       <c r="D24" s="64"/>
       <c r="E24" s="130"/>
       <c r="F24" s="64"/>
-      <c r="G24" s="124"/>
+      <c r="G24" s="135"/>
       <c r="H24" s="63"/>
       <c r="I24" s="64"/>
-      <c r="J24" s="124"/>
+      <c r="J24" s="135"/>
       <c r="K24" s="64"/>
-      <c r="L24" s="126"/>
+      <c r="L24" s="133"/>
       <c r="M24" s="63"/>
       <c r="N24" s="64"/>
-      <c r="O24" s="126"/>
+      <c r="O24" s="133"/>
       <c r="P24" s="63"/>
       <c r="Q24" s="64"/>
       <c r="R24" s="33"/>
@@ -10388,15 +10435,15 @@
       <c r="D25" s="64"/>
       <c r="E25" s="130"/>
       <c r="F25" s="64"/>
-      <c r="G25" s="124"/>
+      <c r="G25" s="135"/>
       <c r="H25" s="63"/>
       <c r="I25" s="64"/>
-      <c r="J25" s="124"/>
+      <c r="J25" s="135"/>
       <c r="K25" s="64"/>
-      <c r="L25" s="126"/>
+      <c r="L25" s="133"/>
       <c r="M25" s="63"/>
       <c r="N25" s="64"/>
-      <c r="O25" s="126"/>
+      <c r="O25" s="133"/>
       <c r="P25" s="63"/>
       <c r="Q25" s="64"/>
       <c r="R25" s="33"/>
@@ -10416,15 +10463,15 @@
       <c r="D26" s="64"/>
       <c r="E26" s="130"/>
       <c r="F26" s="64"/>
-      <c r="G26" s="124"/>
+      <c r="G26" s="135"/>
       <c r="H26" s="63"/>
       <c r="I26" s="64"/>
-      <c r="J26" s="124"/>
+      <c r="J26" s="135"/>
       <c r="K26" s="64"/>
-      <c r="L26" s="126"/>
+      <c r="L26" s="133"/>
       <c r="M26" s="63"/>
       <c r="N26" s="64"/>
-      <c r="O26" s="126"/>
+      <c r="O26" s="133"/>
       <c r="P26" s="63"/>
       <c r="Q26" s="64"/>
       <c r="R26" s="33"/>
@@ -10444,15 +10491,15 @@
       <c r="D27" s="64"/>
       <c r="E27" s="130"/>
       <c r="F27" s="64"/>
-      <c r="G27" s="124"/>
+      <c r="G27" s="135"/>
       <c r="H27" s="63"/>
       <c r="I27" s="64"/>
-      <c r="J27" s="124"/>
+      <c r="J27" s="135"/>
       <c r="K27" s="64"/>
-      <c r="L27" s="126"/>
+      <c r="L27" s="133"/>
       <c r="M27" s="63"/>
       <c r="N27" s="64"/>
-      <c r="O27" s="126"/>
+      <c r="O27" s="133"/>
       <c r="P27" s="63"/>
       <c r="Q27" s="64"/>
       <c r="R27" s="33"/>
@@ -10472,15 +10519,15 @@
       <c r="D28" s="64"/>
       <c r="E28" s="130"/>
       <c r="F28" s="64"/>
-      <c r="G28" s="124"/>
+      <c r="G28" s="135"/>
       <c r="H28" s="63"/>
       <c r="I28" s="64"/>
-      <c r="J28" s="124"/>
+      <c r="J28" s="135"/>
       <c r="K28" s="64"/>
-      <c r="L28" s="126"/>
+      <c r="L28" s="133"/>
       <c r="M28" s="63"/>
       <c r="N28" s="64"/>
-      <c r="O28" s="126"/>
+      <c r="O28" s="133"/>
       <c r="P28" s="63"/>
       <c r="Q28" s="64"/>
       <c r="R28" s="33"/>
@@ -10500,15 +10547,15 @@
       <c r="D29" s="64"/>
       <c r="E29" s="130"/>
       <c r="F29" s="64"/>
-      <c r="G29" s="124"/>
+      <c r="G29" s="135"/>
       <c r="H29" s="63"/>
       <c r="I29" s="64"/>
-      <c r="J29" s="124"/>
+      <c r="J29" s="135"/>
       <c r="K29" s="64"/>
-      <c r="L29" s="126"/>
+      <c r="L29" s="133"/>
       <c r="M29" s="63"/>
       <c r="N29" s="64"/>
-      <c r="O29" s="126"/>
+      <c r="O29" s="133"/>
       <c r="P29" s="63"/>
       <c r="Q29" s="64"/>
       <c r="R29" s="33"/>
@@ -10528,15 +10575,15 @@
       <c r="D30" s="64"/>
       <c r="E30" s="130"/>
       <c r="F30" s="64"/>
-      <c r="G30" s="124"/>
+      <c r="G30" s="135"/>
       <c r="H30" s="63"/>
       <c r="I30" s="64"/>
-      <c r="J30" s="124"/>
+      <c r="J30" s="135"/>
       <c r="K30" s="64"/>
-      <c r="L30" s="126"/>
+      <c r="L30" s="133"/>
       <c r="M30" s="63"/>
       <c r="N30" s="64"/>
-      <c r="O30" s="126"/>
+      <c r="O30" s="133"/>
       <c r="P30" s="63"/>
       <c r="Q30" s="64"/>
       <c r="R30" s="33"/>
@@ -10550,23 +10597,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="125"/>
-      <c r="K31" s="92"/>
-      <c r="L31" s="127"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="127"/>
-      <c r="P31" s="91"/>
-      <c r="Q31" s="92"/>
+      <c r="A31" s="131"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="132"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="83"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11564,6 +11611,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11588,118 +11747,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11709,7 +11756,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5CECE2-1A29-4C94-94D4-07CF7FB29E2C}">
-  <dimension ref="B1:I47"/>
+  <dimension ref="B1:I59"/>
   <sheetFormatPr defaultRowHeight="13" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="1.6328125" customWidth="1"/>
@@ -11722,7 +11769,7 @@
   <sheetData>
     <row r="1" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="2" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F2" s="138" t="s">
+      <c r="F2" s="143" t="s">
         <v>136</v>
       </c>
       <c r="H2" s="54"/>
@@ -11731,7 +11778,7 @@
       </c>
     </row>
     <row r="3" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F3" s="139"/>
+      <c r="F3" s="144"/>
       <c r="H3" s="56" t="s">
         <v>134</v>
       </c>
@@ -11740,7 +11787,7 @@
       </c>
     </row>
     <row r="4" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="F4" s="140"/>
+      <c r="F4" s="145"/>
       <c r="H4" s="58" t="s">
         <v>134</v>
       </c>
@@ -11766,10 +11813,10 @@
     </row>
     <row r="7" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="8" spans="6:9" ht="13" customHeight="1">
-      <c r="H8" s="134" t="s">
+      <c r="H8" s="139" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="135"/>
+      <c r="I8" s="140"/>
     </row>
     <row r="9" spans="6:9" ht="13" customHeight="1">
       <c r="H9" s="40" t="s">
@@ -11997,10 +12044,10 @@
     </row>
     <row r="37" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="38" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H38" s="136" t="s">
+      <c r="H38" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="I38" s="137"/>
+      <c r="I38" s="142"/>
     </row>
     <row r="39" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="H39" s="48" t="s">
@@ -12036,10 +12083,10 @@
     </row>
     <row r="43" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
     <row r="44" spans="2:9" ht="13" customHeight="1">
-      <c r="B44" s="134" t="s">
+      <c r="B44" s="139" t="s">
         <v>126</v>
       </c>
-      <c r="C44" s="135"/>
+      <c r="C44" s="140"/>
     </row>
     <row r="45" spans="2:9" ht="2" customHeight="1">
       <c r="B45" s="52"/>
@@ -12052,6 +12099,9 @@
       <c r="C46" s="43" t="s">
         <v>127</v>
       </c>
+      <c r="I46" s="39" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="47" spans="2:9" ht="13" customHeight="1" thickBot="1">
       <c r="B47" s="46" t="s">
@@ -12059,6 +12109,108 @@
       </c>
       <c r="C47" s="47" t="s">
         <v>137</v>
+      </c>
+      <c r="H47" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I47" s="39" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="13" customHeight="1">
+      <c r="H48" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="8:9" ht="13" customHeight="1">
+      <c r="H49" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I49" s="39" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="8:9" ht="13" customHeight="1">
+      <c r="H50" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I50" s="39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="8:9" ht="13" customHeight="1">
+      <c r="H51" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I51" s="39" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="8:9" ht="13" customHeight="1">
+      <c r="H52" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I52" s="39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="8:9" ht="13" customHeight="1">
+      <c r="H53" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I53" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="8:9" ht="13" customHeight="1">
+      <c r="H54" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I54" s="38" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="8:9" ht="13" customHeight="1">
+      <c r="H55" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I55" s="38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="8:9" ht="13" customHeight="1">
+      <c r="H56" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I56" s="39" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="8:9" ht="13" customHeight="1">
+      <c r="H57" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I57" s="39" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" spans="8:9" ht="13" customHeight="1">
+      <c r="H58" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I58" s="39" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="8:9" ht="13" customHeight="1">
+      <c r="H59" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I59" s="39" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AED9A7F-69EB-4040-96B9-D865BB79BA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32C8CC6-6390-4BA8-8958-2FFA1CE9022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId3"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="クラス" sheetId="8" r:id="rId6"/>
+    <sheet name="クラス" sheetId="8" state="hidden" r:id="rId6"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" state="hidden" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="193">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -134,10 +134,6 @@
   </si>
   <si>
     <t>value</t>
-  </si>
-  <si>
-    <t>テスト仕様書兼
-結果報告書</t>
   </si>
   <si>
     <t>テストレベル</t>
@@ -832,6 +828,198 @@
   </si>
   <si>
     <t>setUserName(userName:String):void</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>userId:String</t>
+  </si>
+  <si>
+    <t>password:String</t>
+  </si>
+  <si>
+    <t>userName:String</t>
+  </si>
+  <si>
+    <t>categoryId:int</t>
+  </si>
+  <si>
+    <t>categoryName:String</t>
+  </si>
+  <si>
+    <t>statusCode:String</t>
+  </si>
+  <si>
+    <t>statusName:String</t>
+  </si>
+  <si>
+    <t>taskId:int</t>
+  </si>
+  <si>
+    <t>taskName:String</t>
+  </si>
+  <si>
+    <t>limitDate:Date</t>
+  </si>
+  <si>
+    <t>memo:String</t>
+  </si>
+  <si>
+    <t>createDatetime:Timestamp</t>
+  </si>
+  <si>
+    <t>updateDatetime:Timestamp</t>
+  </si>
+  <si>
+    <t>UserStatusCategoryTaskBean</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>UserStatusCategoryTaskBean()</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>getCategoryId():int</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>setCategoryId(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>categoryId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:int):void</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>getCategoryName():String</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>setCategoryName(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>categoryName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:String):void</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>setStatusCode(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>statusCode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:String):void</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>getStatusName():String</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>setStatusName(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>statusName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:String):void</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>setTaskId(taskId:int):void</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>setUpdateDatetime(updatetime:Timestamp):void</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>setCreateDatetime(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>createDatetime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:Timestamp):void</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>テスト仕様書兼
+結果報告書</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2134,31 +2322,118 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2167,138 +2442,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2308,35 +2496,35 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2380,23 +2568,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28015</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>56029</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1118101</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>118139</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>905809</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>143586</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F156B090-F720-D488-4B07-F035C9520272}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{703B31BE-7D66-1571-331D-02D5E46A3DE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2405,15 +2593,21 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="886047"/>
-          <a:ext cx="9181124" cy="4504069"/>
+          <a:off x="382868" y="952500"/>
+          <a:ext cx="7423897" cy="4532557"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3103,7 +3297,7 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" s="66"/>
       <c r="G8" s="66"/>
@@ -4172,19 +4366,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="105" t="s">
+      <c r="A1" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="93"/>
-      <c r="F1" s="105" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="93"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -4196,192 +4390,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="96"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
         <v>45705</v>
       </c>
-      <c r="I2" s="99" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="102"/>
+      <c r="I2" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="96"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="103"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="76"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="106" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="87" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="63"/>
       <c r="C6" s="64"/>
-      <c r="D6" s="77" t="s">
-        <v>68</v>
+      <c r="D6" s="88" t="s">
+        <v>67</v>
       </c>
       <c r="E6" s="63"/>
       <c r="F6" s="63"/>
       <c r="G6" s="63"/>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
-      <c r="J6" s="78"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="87" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="63"/>
       <c r="C7" s="64"/>
-      <c r="D7" s="77" t="s">
-        <v>69</v>
+      <c r="D7" s="88" t="s">
+        <v>68</v>
       </c>
       <c r="E7" s="63"/>
       <c r="F7" s="63"/>
       <c r="G7" s="63"/>
       <c r="H7" s="63"/>
       <c r="I7" s="63"/>
-      <c r="J7" s="78"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="87" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="63"/>
       <c r="C8" s="64"/>
-      <c r="D8" s="77" t="s">
-        <v>75</v>
+      <c r="D8" s="88" t="s">
+        <v>74</v>
       </c>
       <c r="E8" s="63"/>
       <c r="F8" s="63"/>
       <c r="G8" s="63"/>
       <c r="H8" s="63"/>
       <c r="I8" s="63"/>
-      <c r="J8" s="78"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="86" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="64"/>
-      <c r="D9" s="79" t="s">
-        <v>158</v>
+      <c r="D9" s="108" t="s">
+        <v>157</v>
       </c>
       <c r="E9" s="63"/>
       <c r="F9" s="63"/>
       <c r="G9" s="63"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
-      <c r="J9" s="78"/>
+      <c r="J9" s="89"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="96"/>
-      <c r="B10" s="98" t="s">
+      <c r="A10" s="102"/>
+      <c r="B10" s="86" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="64"/>
-      <c r="D10" s="79" t="s">
-        <v>128</v>
+      <c r="D10" s="108" t="s">
+        <v>127</v>
       </c>
       <c r="E10" s="63"/>
       <c r="F10" s="63"/>
       <c r="G10" s="63"/>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
-      <c r="J10" s="78"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="97"/>
-      <c r="B11" s="98" t="s">
+      <c r="A11" s="103"/>
+      <c r="B11" s="86" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="64"/>
       <c r="D11" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="81"/>
+        <v>72</v>
+      </c>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="110"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="87" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
-      <c r="D12" s="77" t="s">
-        <v>71</v>
+      <c r="D12" s="88" t="s">
+        <v>70</v>
       </c>
       <c r="E12" s="63"/>
       <c r="F12" s="63"/>
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
-      <c r="J12" s="78"/>
+      <c r="J12" s="89"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="71" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="73"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5372,17 +5566,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5391,14 +5582,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5420,16 +5614,16 @@
       <c r="A1" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="105" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="93"/>
-      <c r="F1" s="105" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="93"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5441,46 +5635,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="96"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="106" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
         <v>45706</v>
       </c>
-      <c r="I2" s="99" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="102"/>
+      <c r="I2" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="96"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="103"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6831,16 +7025,16 @@
       <c r="A1" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="105" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="93"/>
-      <c r="F1" s="105" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="93"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6852,46 +7046,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="96"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="106" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
         <v>45707</v>
       </c>
-      <c r="I2" s="99" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="102"/>
+      <c r="I2" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="96"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="103"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8254,16 +8448,16 @@
       <c r="A1" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="105" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="93"/>
-      <c r="F1" s="105" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="93"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8275,65 +8469,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="96"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="106" t="s">
+      <c r="C2" s="76"/>
+      <c r="D2" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="74"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="79">
+        <v>45706</v>
+      </c>
+      <c r="I2" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="83"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="96"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="84"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="96"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="84"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="112" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="100"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="116" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="110">
-        <v>45706</v>
-      </c>
-      <c r="I2" s="99" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="102"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="103"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="103"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="121" t="s">
-        <v>144</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="76"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="114" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="63"/>
@@ -8344,22 +8538,22 @@
       <c r="G6" s="63"/>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
-      <c r="J6" s="78"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="122"/>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="124"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="87"/>
+      <c r="A8" s="96"/>
       <c r="B8" s="66"/>
       <c r="C8" s="66"/>
       <c r="D8" s="66"/>
@@ -8368,10 +8562,10 @@
       <c r="G8" s="66"/>
       <c r="H8" s="66"/>
       <c r="I8" s="66"/>
-      <c r="J8" s="125"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="87"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
       <c r="D9" s="66"/>
@@ -8380,10 +8574,10 @@
       <c r="G9" s="66"/>
       <c r="H9" s="66"/>
       <c r="I9" s="66"/>
-      <c r="J9" s="125"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="87"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
       <c r="D10" s="66"/>
@@ -8392,10 +8586,10 @@
       <c r="G10" s="66"/>
       <c r="H10" s="66"/>
       <c r="I10" s="66"/>
-      <c r="J10" s="125"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="87"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
       <c r="D11" s="66"/>
@@ -8404,10 +8598,10 @@
       <c r="G11" s="66"/>
       <c r="H11" s="66"/>
       <c r="I11" s="66"/>
-      <c r="J11" s="125"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="87"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
       <c r="D12" s="66"/>
@@ -8416,10 +8610,10 @@
       <c r="G12" s="66"/>
       <c r="H12" s="66"/>
       <c r="I12" s="66"/>
-      <c r="J12" s="125"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="87"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -8428,44 +8622,44 @@
       <c r="G13" s="66"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
-      <c r="J13" s="125"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="112" t="s">
+      <c r="A14" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="113"/>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="114"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="121"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="112" t="s">
+      <c r="A15" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="88" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="125"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="112" t="s">
+      <c r="A16" s="114" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="63"/>
@@ -8486,125 +8680,125 @@
         <v>18</v>
       </c>
       <c r="I16" s="63"/>
-      <c r="J16" s="78"/>
+      <c r="J16" s="89"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="118" t="s">
-        <v>146</v>
+      <c r="A17" s="115" t="s">
+        <v>145</v>
       </c>
       <c r="B17" s="63"/>
       <c r="C17" s="64"/>
       <c r="D17" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H17" s="77" t="s">
-        <v>153</v>
+      <c r="H17" s="88" t="s">
+        <v>152</v>
       </c>
       <c r="I17" s="63"/>
-      <c r="J17" s="78"/>
+      <c r="J17" s="89"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="112" t="s">
+      <c r="A18" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="113"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="114"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="113"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="116"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="88" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="125"/>
       <c r="I19" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="118" t="s">
-        <v>150</v>
+      <c r="A20" s="115" t="s">
+        <v>149</v>
       </c>
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
       <c r="D20" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F20" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="77" t="s">
-        <v>157</v>
+      <c r="H20" s="88" t="s">
+        <v>156</v>
       </c>
       <c r="I20" s="63"/>
-      <c r="J20" s="78"/>
+      <c r="J20" s="89"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="118"/>
+      <c r="A21" s="115"/>
       <c r="B21" s="63"/>
       <c r="C21" s="64"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="77"/>
+      <c r="H21" s="88"/>
       <c r="I21" s="63"/>
-      <c r="J21" s="78"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="118"/>
+      <c r="A22" s="115"/>
       <c r="B22" s="63"/>
       <c r="C22" s="64"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="77"/>
+      <c r="H22" s="88"/>
       <c r="I22" s="63"/>
-      <c r="J22" s="78"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="120"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="83"/>
+      <c r="A23" s="113"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="73"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="105"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9585,11 +9779,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9606,15 +9804,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9635,80 +9829,80 @@
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" customHeight="1">
       <c r="A1" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="D1" s="38" t="s">
         <v>78</v>
-      </c>
-      <c r="D1" s="38" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1">
       <c r="A2" s="127" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="C2" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="60" t="s">
         <v>81</v>
-      </c>
-      <c r="C2" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1">
       <c r="A3" s="127"/>
       <c r="B3" s="128" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1">
       <c r="A4" s="127"/>
       <c r="B4" s="128"/>
       <c r="C4" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="39" t="s">
         <v>86</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.5" customHeight="1">
       <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="C5" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="D5" s="38" t="s">
         <v>90</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.5" customHeight="1">
       <c r="A6" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="C6" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="D6" s="38" t="s">
         <v>94</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -9733,141 +9927,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="105" t="s">
+      <c r="A1" s="93" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="105" t="s">
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="105" t="s">
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="105" t="s">
+      <c r="P1" s="72"/>
+      <c r="Q1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="93"/>
-      <c r="S1" s="105" t="s">
+      <c r="R1" s="72"/>
+      <c r="S1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="76"/>
+      <c r="T1" s="107"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
+      <c r="A2" s="96"/>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
       <c r="D2" s="66"/>
       <c r="E2" s="66"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="107"/>
-      <c r="S2" s="106"/>
-      <c r="T2" s="124"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="119"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="96"/>
       <c r="B3" s="66"/>
       <c r="C3" s="66"/>
       <c r="D3" s="66"/>
       <c r="E3" s="66"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="108"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="75"/>
       <c r="H3" s="66"/>
       <c r="I3" s="66"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="108"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="75"/>
       <c r="L3" s="66"/>
       <c r="M3" s="66"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="125"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="120"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="109"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="109"/>
-      <c r="T4" s="137"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="133"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="74" t="s">
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="107"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="114" t="s">
         <v>34</v>
-      </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="76"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="112" t="s">
-        <v>35</v>
       </c>
       <c r="B6" s="63"/>
       <c r="C6" s="63"/>
       <c r="D6" s="63"/>
       <c r="E6" s="63"/>
       <c r="F6" s="64"/>
-      <c r="G6" s="77" t="s">
+      <c r="G6" s="88" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="63"/>
@@ -9882,19 +10076,19 @@
       <c r="Q6" s="63"/>
       <c r="R6" s="63"/>
       <c r="S6" s="63"/>
-      <c r="T6" s="78"/>
+      <c r="T6" s="89"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="112" t="s">
-        <v>36</v>
+      <c r="A7" s="114" t="s">
+        <v>35</v>
       </c>
       <c r="B7" s="63"/>
       <c r="C7" s="63"/>
       <c r="D7" s="63"/>
       <c r="E7" s="63"/>
       <c r="F7" s="64"/>
-      <c r="G7" s="77" t="s">
-        <v>37</v>
+      <c r="G7" s="88" t="s">
+        <v>36</v>
       </c>
       <c r="H7" s="63"/>
       <c r="I7" s="63"/>
@@ -9908,7 +10102,7 @@
       <c r="Q7" s="63"/>
       <c r="R7" s="63"/>
       <c r="S7" s="63"/>
-      <c r="T7" s="78"/>
+      <c r="T7" s="89"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9936,11 +10130,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -9970,7 +10164,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -10000,7 +10194,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -10030,7 +10224,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -10060,7 +10254,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -10107,76 +10301,76 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="112" t="s">
-        <v>44</v>
+      <c r="A15" s="114" t="s">
+        <v>43</v>
       </c>
       <c r="B15" s="64"/>
       <c r="C15" s="136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="64"/>
       <c r="E15" s="126" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" s="64"/>
       <c r="G15" s="126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" s="63"/>
       <c r="I15" s="64"/>
       <c r="J15" s="126" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K15" s="64"/>
       <c r="L15" s="126" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M15" s="63"/>
       <c r="N15" s="64"/>
       <c r="O15" s="126" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P15" s="63"/>
       <c r="Q15" s="64"/>
       <c r="R15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="134">
+        <v>1</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="135" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="129">
-        <v>1</v>
-      </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="130" t="s">
+      <c r="D16" s="64"/>
+      <c r="E16" s="135" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="130" t="s">
+      <c r="F16" s="64"/>
+      <c r="G16" s="129" t="s">
         <v>54</v>
-      </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="135" t="s">
-        <v>55</v>
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="64"/>
-      <c r="J16" s="135" t="s">
+      <c r="J16" s="129" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="64"/>
+      <c r="L16" s="131" t="s">
         <v>56</v>
-      </c>
-      <c r="K16" s="64"/>
-      <c r="L16" s="133" t="s">
-        <v>57</v>
       </c>
       <c r="M16" s="63"/>
       <c r="N16" s="64"/>
-      <c r="O16" s="133" t="s">
-        <v>58</v>
+      <c r="O16" s="131" t="s">
+        <v>57</v>
       </c>
       <c r="P16" s="63"/>
       <c r="Q16" s="64"/>
@@ -10191,34 +10385,34 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="129">
+      <c r="A17" s="134">
         <v>2</v>
       </c>
       <c r="B17" s="64"/>
-      <c r="C17" s="130" t="s">
+      <c r="C17" s="135" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="64"/>
+      <c r="E17" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="130" t="s">
+      <c r="F17" s="64"/>
+      <c r="G17" s="129" t="s">
         <v>60</v>
-      </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="135" t="s">
-        <v>61</v>
       </c>
       <c r="H17" s="63"/>
       <c r="I17" s="64"/>
-      <c r="J17" s="135" t="s">
+      <c r="J17" s="129" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="64"/>
+      <c r="L17" s="131" t="s">
         <v>62</v>
-      </c>
-      <c r="K17" s="64"/>
-      <c r="L17" s="133" t="s">
-        <v>63</v>
       </c>
       <c r="M17" s="63"/>
       <c r="N17" s="64"/>
-      <c r="O17" s="133" t="s">
-        <v>64</v>
+      <c r="O17" s="131" t="s">
+        <v>63</v>
       </c>
       <c r="P17" s="63"/>
       <c r="Q17" s="64"/>
@@ -10233,21 +10427,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="129"/>
+      <c r="A18" s="134"/>
       <c r="B18" s="64"/>
-      <c r="C18" s="130"/>
+      <c r="C18" s="135"/>
       <c r="D18" s="64"/>
-      <c r="E18" s="130"/>
+      <c r="E18" s="135"/>
       <c r="F18" s="64"/>
-      <c r="G18" s="135"/>
+      <c r="G18" s="129"/>
       <c r="H18" s="63"/>
       <c r="I18" s="64"/>
-      <c r="J18" s="135"/>
+      <c r="J18" s="129"/>
       <c r="K18" s="64"/>
-      <c r="L18" s="133"/>
+      <c r="L18" s="131"/>
       <c r="M18" s="63"/>
       <c r="N18" s="64"/>
-      <c r="O18" s="133"/>
+      <c r="O18" s="131"/>
       <c r="P18" s="63"/>
       <c r="Q18" s="64"/>
       <c r="R18" s="33"/>
@@ -10261,21 +10455,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="129"/>
+      <c r="A19" s="134"/>
       <c r="B19" s="64"/>
-      <c r="C19" s="130"/>
+      <c r="C19" s="135"/>
       <c r="D19" s="64"/>
-      <c r="E19" s="130"/>
+      <c r="E19" s="135"/>
       <c r="F19" s="64"/>
-      <c r="G19" s="135"/>
+      <c r="G19" s="129"/>
       <c r="H19" s="63"/>
       <c r="I19" s="64"/>
-      <c r="J19" s="135"/>
+      <c r="J19" s="129"/>
       <c r="K19" s="64"/>
-      <c r="L19" s="133"/>
+      <c r="L19" s="131"/>
       <c r="M19" s="63"/>
       <c r="N19" s="64"/>
-      <c r="O19" s="133"/>
+      <c r="O19" s="131"/>
       <c r="P19" s="63"/>
       <c r="Q19" s="64"/>
       <c r="R19" s="33"/>
@@ -10289,21 +10483,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="129"/>
+      <c r="A20" s="134"/>
       <c r="B20" s="64"/>
-      <c r="C20" s="130"/>
+      <c r="C20" s="135"/>
       <c r="D20" s="64"/>
-      <c r="E20" s="130"/>
+      <c r="E20" s="135"/>
       <c r="F20" s="64"/>
-      <c r="G20" s="135"/>
+      <c r="G20" s="129"/>
       <c r="H20" s="63"/>
       <c r="I20" s="64"/>
-      <c r="J20" s="135"/>
+      <c r="J20" s="129"/>
       <c r="K20" s="64"/>
-      <c r="L20" s="133"/>
+      <c r="L20" s="131"/>
       <c r="M20" s="63"/>
       <c r="N20" s="64"/>
-      <c r="O20" s="133"/>
+      <c r="O20" s="131"/>
       <c r="P20" s="63"/>
       <c r="Q20" s="64"/>
       <c r="R20" s="33"/>
@@ -10317,21 +10511,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="129"/>
+      <c r="A21" s="134"/>
       <c r="B21" s="64"/>
-      <c r="C21" s="130"/>
+      <c r="C21" s="135"/>
       <c r="D21" s="64"/>
-      <c r="E21" s="130"/>
+      <c r="E21" s="135"/>
       <c r="F21" s="64"/>
-      <c r="G21" s="135"/>
+      <c r="G21" s="129"/>
       <c r="H21" s="63"/>
       <c r="I21" s="64"/>
-      <c r="J21" s="135"/>
+      <c r="J21" s="129"/>
       <c r="K21" s="64"/>
-      <c r="L21" s="133"/>
+      <c r="L21" s="131"/>
       <c r="M21" s="63"/>
       <c r="N21" s="64"/>
-      <c r="O21" s="133"/>
+      <c r="O21" s="131"/>
       <c r="P21" s="63"/>
       <c r="Q21" s="64"/>
       <c r="R21" s="33"/>
@@ -10345,21 +10539,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="129"/>
+      <c r="A22" s="134"/>
       <c r="B22" s="64"/>
-      <c r="C22" s="130"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="64"/>
-      <c r="E22" s="130"/>
+      <c r="E22" s="135"/>
       <c r="F22" s="64"/>
-      <c r="G22" s="135"/>
+      <c r="G22" s="129"/>
       <c r="H22" s="63"/>
       <c r="I22" s="64"/>
-      <c r="J22" s="135"/>
+      <c r="J22" s="129"/>
       <c r="K22" s="64"/>
-      <c r="L22" s="133"/>
+      <c r="L22" s="131"/>
       <c r="M22" s="63"/>
       <c r="N22" s="64"/>
-      <c r="O22" s="133"/>
+      <c r="O22" s="131"/>
       <c r="P22" s="63"/>
       <c r="Q22" s="64"/>
       <c r="R22" s="33"/>
@@ -10373,21 +10567,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="129"/>
+      <c r="A23" s="134"/>
       <c r="B23" s="64"/>
-      <c r="C23" s="130"/>
+      <c r="C23" s="135"/>
       <c r="D23" s="64"/>
-      <c r="E23" s="130"/>
+      <c r="E23" s="135"/>
       <c r="F23" s="64"/>
-      <c r="G23" s="135"/>
+      <c r="G23" s="129"/>
       <c r="H23" s="63"/>
       <c r="I23" s="64"/>
-      <c r="J23" s="135"/>
+      <c r="J23" s="129"/>
       <c r="K23" s="64"/>
-      <c r="L23" s="133"/>
+      <c r="L23" s="131"/>
       <c r="M23" s="63"/>
       <c r="N23" s="64"/>
-      <c r="O23" s="133"/>
+      <c r="O23" s="131"/>
       <c r="P23" s="63"/>
       <c r="Q23" s="64"/>
       <c r="R23" s="33"/>
@@ -10401,21 +10595,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="129"/>
+      <c r="A24" s="134"/>
       <c r="B24" s="64"/>
-      <c r="C24" s="130"/>
+      <c r="C24" s="135"/>
       <c r="D24" s="64"/>
-      <c r="E24" s="130"/>
+      <c r="E24" s="135"/>
       <c r="F24" s="64"/>
-      <c r="G24" s="135"/>
+      <c r="G24" s="129"/>
       <c r="H24" s="63"/>
       <c r="I24" s="64"/>
-      <c r="J24" s="135"/>
+      <c r="J24" s="129"/>
       <c r="K24" s="64"/>
-      <c r="L24" s="133"/>
+      <c r="L24" s="131"/>
       <c r="M24" s="63"/>
       <c r="N24" s="64"/>
-      <c r="O24" s="133"/>
+      <c r="O24" s="131"/>
       <c r="P24" s="63"/>
       <c r="Q24" s="64"/>
       <c r="R24" s="33"/>
@@ -10429,21 +10623,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="129"/>
+      <c r="A25" s="134"/>
       <c r="B25" s="64"/>
-      <c r="C25" s="130"/>
+      <c r="C25" s="135"/>
       <c r="D25" s="64"/>
-      <c r="E25" s="130"/>
+      <c r="E25" s="135"/>
       <c r="F25" s="64"/>
-      <c r="G25" s="135"/>
+      <c r="G25" s="129"/>
       <c r="H25" s="63"/>
       <c r="I25" s="64"/>
-      <c r="J25" s="135"/>
+      <c r="J25" s="129"/>
       <c r="K25" s="64"/>
-      <c r="L25" s="133"/>
+      <c r="L25" s="131"/>
       <c r="M25" s="63"/>
       <c r="N25" s="64"/>
-      <c r="O25" s="133"/>
+      <c r="O25" s="131"/>
       <c r="P25" s="63"/>
       <c r="Q25" s="64"/>
       <c r="R25" s="33"/>
@@ -10457,21 +10651,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="129"/>
+      <c r="A26" s="134"/>
       <c r="B26" s="64"/>
-      <c r="C26" s="130"/>
+      <c r="C26" s="135"/>
       <c r="D26" s="64"/>
-      <c r="E26" s="130"/>
+      <c r="E26" s="135"/>
       <c r="F26" s="64"/>
-      <c r="G26" s="135"/>
+      <c r="G26" s="129"/>
       <c r="H26" s="63"/>
       <c r="I26" s="64"/>
-      <c r="J26" s="135"/>
+      <c r="J26" s="129"/>
       <c r="K26" s="64"/>
-      <c r="L26" s="133"/>
+      <c r="L26" s="131"/>
       <c r="M26" s="63"/>
       <c r="N26" s="64"/>
-      <c r="O26" s="133"/>
+      <c r="O26" s="131"/>
       <c r="P26" s="63"/>
       <c r="Q26" s="64"/>
       <c r="R26" s="33"/>
@@ -10485,21 +10679,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="129"/>
+      <c r="A27" s="134"/>
       <c r="B27" s="64"/>
-      <c r="C27" s="130"/>
+      <c r="C27" s="135"/>
       <c r="D27" s="64"/>
-      <c r="E27" s="130"/>
+      <c r="E27" s="135"/>
       <c r="F27" s="64"/>
-      <c r="G27" s="135"/>
+      <c r="G27" s="129"/>
       <c r="H27" s="63"/>
       <c r="I27" s="64"/>
-      <c r="J27" s="135"/>
+      <c r="J27" s="129"/>
       <c r="K27" s="64"/>
-      <c r="L27" s="133"/>
+      <c r="L27" s="131"/>
       <c r="M27" s="63"/>
       <c r="N27" s="64"/>
-      <c r="O27" s="133"/>
+      <c r="O27" s="131"/>
       <c r="P27" s="63"/>
       <c r="Q27" s="64"/>
       <c r="R27" s="33"/>
@@ -10513,21 +10707,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="129"/>
+      <c r="A28" s="134"/>
       <c r="B28" s="64"/>
-      <c r="C28" s="130"/>
+      <c r="C28" s="135"/>
       <c r="D28" s="64"/>
-      <c r="E28" s="130"/>
+      <c r="E28" s="135"/>
       <c r="F28" s="64"/>
-      <c r="G28" s="135"/>
+      <c r="G28" s="129"/>
       <c r="H28" s="63"/>
       <c r="I28" s="64"/>
-      <c r="J28" s="135"/>
+      <c r="J28" s="129"/>
       <c r="K28" s="64"/>
-      <c r="L28" s="133"/>
+      <c r="L28" s="131"/>
       <c r="M28" s="63"/>
       <c r="N28" s="64"/>
-      <c r="O28" s="133"/>
+      <c r="O28" s="131"/>
       <c r="P28" s="63"/>
       <c r="Q28" s="64"/>
       <c r="R28" s="33"/>
@@ -10541,21 +10735,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="129"/>
+      <c r="A29" s="134"/>
       <c r="B29" s="64"/>
-      <c r="C29" s="130"/>
+      <c r="C29" s="135"/>
       <c r="D29" s="64"/>
-      <c r="E29" s="130"/>
+      <c r="E29" s="135"/>
       <c r="F29" s="64"/>
-      <c r="G29" s="135"/>
+      <c r="G29" s="129"/>
       <c r="H29" s="63"/>
       <c r="I29" s="64"/>
-      <c r="J29" s="135"/>
+      <c r="J29" s="129"/>
       <c r="K29" s="64"/>
-      <c r="L29" s="133"/>
+      <c r="L29" s="131"/>
       <c r="M29" s="63"/>
       <c r="N29" s="64"/>
-      <c r="O29" s="133"/>
+      <c r="O29" s="131"/>
       <c r="P29" s="63"/>
       <c r="Q29" s="64"/>
       <c r="R29" s="33"/>
@@ -10569,21 +10763,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="129"/>
+      <c r="A30" s="134"/>
       <c r="B30" s="64"/>
-      <c r="C30" s="130"/>
+      <c r="C30" s="135"/>
       <c r="D30" s="64"/>
-      <c r="E30" s="130"/>
+      <c r="E30" s="135"/>
       <c r="F30" s="64"/>
-      <c r="G30" s="135"/>
+      <c r="G30" s="129"/>
       <c r="H30" s="63"/>
       <c r="I30" s="64"/>
-      <c r="J30" s="135"/>
+      <c r="J30" s="129"/>
       <c r="K30" s="64"/>
-      <c r="L30" s="133"/>
+      <c r="L30" s="131"/>
       <c r="M30" s="63"/>
       <c r="N30" s="64"/>
-      <c r="O30" s="133"/>
+      <c r="O30" s="131"/>
       <c r="P30" s="63"/>
       <c r="Q30" s="64"/>
       <c r="R30" s="33"/>
@@ -10597,23 +10791,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="131"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="132"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="134"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="134"/>
-      <c r="P31" s="72"/>
-      <c r="Q31" s="83"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="130"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="132"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="132"/>
+      <c r="P31" s="91"/>
+      <c r="Q31" s="92"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11611,62 +11805,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11691,62 +11885,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11756,7 +11950,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5CECE2-1A29-4C94-94D4-07CF7FB29E2C}">
-  <dimension ref="B1:I59"/>
+  <dimension ref="B1:L59"/>
   <sheetFormatPr defaultRowHeight="13" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="1.6328125" customWidth="1"/>
@@ -11765,452 +11959,699 @@
     <col min="6" max="6" width="30.6328125" customWidth="1"/>
     <col min="8" max="8" width="1.6328125" customWidth="1"/>
     <col min="9" max="9" width="60.6328125" customWidth="1"/>
+    <col min="11" max="11" width="1.6328125" customWidth="1"/>
+    <col min="12" max="12" width="60.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
-    <row r="2" spans="6:9" ht="13" customHeight="1" thickBot="1">
+    <row r="1" spans="6:12" ht="13" customHeight="1" thickBot="1"/>
+    <row r="2" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="F2" s="143" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H2" s="54"/>
       <c r="I2" s="55" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="6:9" ht="13" customHeight="1" thickBot="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="F3" s="144"/>
       <c r="H3" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I3" s="57" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="6:9" ht="13" customHeight="1" thickBot="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="F4" s="145"/>
       <c r="H4" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="6:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H5" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="59" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="6:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H6" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="6:12" ht="13" customHeight="1" thickBot="1"/>
+    <row r="8" spans="6:12" ht="13" customHeight="1">
+      <c r="H8" s="139" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="140"/>
+      <c r="L8" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="6:12" ht="13" customHeight="1">
+      <c r="H9" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="6:12" ht="13" customHeight="1">
+      <c r="H10" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="K10" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="6:12" ht="13" customHeight="1">
+      <c r="H11" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="6:12" ht="13" customHeight="1">
+      <c r="H12" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="6:12" ht="13" customHeight="1">
+      <c r="H13" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="6:12" ht="13" customHeight="1">
+      <c r="H14" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="K14" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="6:12" ht="13" customHeight="1">
+      <c r="H15" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="6:12" ht="13" customHeight="1">
+      <c r="H16" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="8:12" ht="13" customHeight="1">
+      <c r="H17" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="8:12" ht="13" customHeight="1">
+      <c r="H18" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="K18" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="8:12" ht="13" customHeight="1">
+      <c r="H19" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="8:12" ht="13" customHeight="1">
+      <c r="H20" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="8:12" ht="13" customHeight="1">
+      <c r="H21" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="8:12" ht="13" customHeight="1">
+      <c r="H22" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="K22" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L22" s="39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="8:12" ht="13" customHeight="1">
+      <c r="H23" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L23" s="39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="8:12" ht="13" customHeight="1">
+      <c r="H24" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L24" s="39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="8:12" ht="13" customHeight="1">
+      <c r="H25" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="K25" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L25" s="39" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="8:12" ht="13" customHeight="1">
+      <c r="H26" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I26" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="K26" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L26" s="39" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="8:12" ht="13" customHeight="1">
+      <c r="H27" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I27" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="K27" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L27" s="39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="8:12" ht="13" customHeight="1">
+      <c r="H28" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I28" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="K28" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L28" s="39" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="8:12" ht="13" customHeight="1">
+      <c r="H29" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I29" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L29" s="39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="8:12" ht="13" customHeight="1">
+      <c r="H30" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I30" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="K30" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" s="39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="8:12" ht="13" customHeight="1">
+      <c r="H31" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I31" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="K31" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L31" s="39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="8:12" ht="13" customHeight="1">
+      <c r="H32" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="K32" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L32" s="39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" ht="13" customHeight="1">
+      <c r="H33" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L33" s="39" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" ht="13" customHeight="1">
+      <c r="H34" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I34" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="K34" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L34" s="39" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" ht="13" customHeight="1">
+      <c r="H35" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I35" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="K35" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L35" s="39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H36" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="K36" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L36" s="39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="K37" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L37" s="39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H38" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="I38" s="142"/>
+      <c r="K38" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L38" s="39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H39" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="I39" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="K39" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L39" s="39" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H40" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="I40" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="K40" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L40" s="39" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H41" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="I41" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="K41" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L41" s="39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="H42" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="59" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H5" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="I5" s="59" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="6:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H6" s="56" t="s">
-        <v>134</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="6:9" ht="13" customHeight="1" thickBot="1"/>
-    <row r="8" spans="6:9" ht="13" customHeight="1">
-      <c r="H8" s="139" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" s="140"/>
-    </row>
-    <row r="9" spans="6:9" ht="13" customHeight="1">
-      <c r="H9" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="6:9" ht="13" customHeight="1">
-      <c r="H10" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="6:9" ht="13" customHeight="1">
-      <c r="H11" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="I11" s="43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="6:9" ht="13" customHeight="1">
-      <c r="H12" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="6:9" ht="13" customHeight="1">
-      <c r="H13" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="43" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="6:9" ht="13" customHeight="1">
-      <c r="H14" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="I14" s="43" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="6:9" ht="13" customHeight="1">
-      <c r="H15" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" s="43" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="6:9" ht="13" customHeight="1">
-      <c r="H16" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="8:9" ht="13" customHeight="1">
-      <c r="H17" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" s="45" t="s">
+      <c r="K42" s="39" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="18" spans="8:9" ht="13" customHeight="1">
-      <c r="H18" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="8:9" ht="13" customHeight="1">
-      <c r="H19" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="43" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="8:9" ht="13" customHeight="1">
-      <c r="H20" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="43" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="8:9" ht="13" customHeight="1">
-      <c r="H21" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="43" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="8:9" ht="13" customHeight="1">
-      <c r="H22" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" s="43" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="8:9" ht="13" customHeight="1">
-      <c r="H23" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="43" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" spans="8:9" ht="13" customHeight="1">
-      <c r="H24" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" s="43" t="s">
+      <c r="L42" s="39" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="8:9" ht="13" customHeight="1">
-      <c r="H25" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="43" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="8:9" ht="13" customHeight="1">
-      <c r="H26" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="43" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="8:9" ht="13" customHeight="1">
-      <c r="H27" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I27" s="43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="8:9" ht="13" customHeight="1">
-      <c r="H28" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I28" s="43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="8:9" ht="13" customHeight="1">
-      <c r="H29" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I29" s="43" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="8:9" ht="13" customHeight="1">
-      <c r="H30" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I30" s="43" t="s">
+    <row r="43" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="K43" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L43" s="39" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="8:9" ht="13" customHeight="1">
-      <c r="H31" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I31" s="43" t="s">
+    <row r="44" spans="2:12" ht="13" customHeight="1">
+      <c r="B44" s="139" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="140"/>
+      <c r="K44" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L44" s="39" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="8:9" ht="13" customHeight="1">
-      <c r="H32" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I32" s="43" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="13" customHeight="1">
-      <c r="H33" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I33" s="43" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="13" customHeight="1">
-      <c r="H34" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I34" s="43" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" ht="13" customHeight="1">
-      <c r="H35" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I35" s="43" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H36" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="47" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
-    <row r="38" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H38" s="141" t="s">
-        <v>129</v>
-      </c>
-      <c r="I38" s="142"/>
-    </row>
-    <row r="39" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H39" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="I39" s="49" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H40" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="I40" s="49" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H41" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="H42" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="I42" s="51" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" ht="13" customHeight="1" thickBot="1"/>
-    <row r="44" spans="2:9" ht="13" customHeight="1">
-      <c r="B44" s="139" t="s">
-        <v>126</v>
-      </c>
-      <c r="C44" s="140"/>
-    </row>
-    <row r="45" spans="2:9" ht="2" customHeight="1">
+    <row r="45" spans="2:12" ht="12" customHeight="1">
       <c r="B45" s="52"/>
       <c r="C45" s="53"/>
-    </row>
-    <row r="46" spans="2:9" ht="13" customHeight="1">
+      <c r="K45" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L45" s="39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" ht="13" customHeight="1">
       <c r="B46" s="42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" s="43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I46" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="K46" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L46" s="39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" ht="13" customHeight="1" thickBot="1">
+      <c r="B47" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="H47" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="I47" s="39" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="47" spans="2:9" ht="13" customHeight="1" thickBot="1">
-      <c r="B47" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="H47" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="I47" s="39" t="s">
+      <c r="K47" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L47" s="39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" ht="13" customHeight="1">
+      <c r="H48" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="I48" s="38" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="48" spans="2:9" ht="13" customHeight="1">
-      <c r="H48" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="I48" s="38" t="s">
-        <v>161</v>
+      <c r="K48" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="L48" s="39" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="8:9" ht="13" customHeight="1">
       <c r="H49" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I49" s="39" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="8:9" ht="13" customHeight="1">
       <c r="H50" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I50" s="39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="8:9" ht="13" customHeight="1">
       <c r="H51" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I51" s="39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="8:9" ht="13" customHeight="1">
       <c r="H52" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I52" s="39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="8:9" ht="13" customHeight="1">
       <c r="H53" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I53" s="39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="8:9" ht="13" customHeight="1">
       <c r="H54" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I54" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="8:9" ht="13" customHeight="1">
       <c r="H55" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I55" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="8:9" ht="13" customHeight="1">
       <c r="H56" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I56" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="8:9" ht="13" customHeight="1">
       <c r="H57" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I57" s="39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="8:9" ht="13" customHeight="1">
       <c r="H58" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I58" s="39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="8:9" ht="13" customHeight="1">
       <c r="H59" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I59" s="39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/詳細設計図/タスク一覧機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク一覧機能_詳細設計図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sensh\Documents\mytask\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32C8CC6-6390-4BA8-8958-2FFA1CE9022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BC7CF7-1510-4556-9E61-D5E548A243D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,11 @@
     <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId3"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId4"/>
-    <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
+    <sheet name="画面設計書(タスク一覧表示画面)" sheetId="5" r:id="rId5"/>
     <sheet name="クラス" sheetId="8" state="hidden" r:id="rId6"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="9" state="hidden" r:id="rId8"/>
+    <sheet name="画面設計書(ユーザー認証失敗画面) " sheetId="10" r:id="rId7"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="197">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -586,12 +587,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>Alt-4該当タスクを登録していないユーザが「タスク削除」または「タスク編集」ボタンを押下した場合
-1.システムは「タスク登録者のみ編集・削除が可能です。」というエラーメッセージを表示する。
-2.①に戻る</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ConnectionManager</t>
   </si>
   <si>
@@ -1020,6 +1015,46 @@
   <si>
     <t>テスト仕様書兼
 結果報告書</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Alt-4該当タスクを登録していないユーザが「タスク削除」または「タスク編集」ボタンを押下した場合
+1.システムは「タスクの編集・削除はタスクを登録したユーザーのみ可能です。」というエラーメッセージを表示する。
+2.①に戻る</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザー認証失敗画面</t>
+    <rPh sb="4" eb="8">
+      <t>ニンショウシッパイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>taskList</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク一覧表示画面へ</t>
+    <rPh sb="3" eb="7">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク一覧表示画面へ遷移する。</t>
+    <rPh sb="3" eb="9">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2108,7 +2143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2322,12 +2357,111 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2337,126 +2471,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2472,21 +2522,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2496,36 +2531,36 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2545,6 +2580,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2948,6 +2992,263 @@
         <a:xfrm>
           <a:off x="6503253" y="3141325"/>
           <a:ext cx="1085135" cy="494118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>　</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>491369</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>220569</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1951B435-D03C-1FF8-DEC7-FEDEBA7FDCA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1534584"/>
+          <a:ext cx="5072440" cy="1808068"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>241904</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>710595</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>214382</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D057699-C5B2-4AEA-A0FB-401203904451}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2834821"/>
+          <a:ext cx="1776488" cy="501644"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>236408</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>246028</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>149817</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>210979</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="テキスト ボックス 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7639F846-7B5A-4D3C-8503-1A8F273226A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1302301" y="2574361"/>
+          <a:ext cx="1085135" cy="494118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>①　</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>750455</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19242</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>663864</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>14431</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC974C02-2626-4A8B-8CB7-D00F8BD25C21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14733155" y="3410142"/>
+          <a:ext cx="605559" cy="490489"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4366,19 +4667,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -4390,70 +4691,70 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45705</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="106" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="94" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="63"/>
       <c r="C6" s="64"/>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="77" t="s">
         <v>67</v>
       </c>
       <c r="E6" s="63"/>
@@ -4461,15 +4762,15 @@
       <c r="G6" s="63"/>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
-      <c r="J6" s="89"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="94" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="63"/>
       <c r="C7" s="64"/>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="77" t="s">
         <v>68</v>
       </c>
       <c r="E7" s="63"/>
@@ -4477,15 +4778,15 @@
       <c r="G7" s="63"/>
       <c r="H7" s="63"/>
       <c r="I7" s="63"/>
-      <c r="J7" s="89"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="94" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="63"/>
       <c r="C8" s="64"/>
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="77" t="s">
         <v>74</v>
       </c>
       <c r="E8" s="63"/>
@@ -4493,65 +4794,65 @@
       <c r="G8" s="63"/>
       <c r="H8" s="63"/>
       <c r="I8" s="63"/>
-      <c r="J8" s="89"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="98" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="64"/>
-      <c r="D9" s="108" t="s">
-        <v>157</v>
+      <c r="D9" s="79" t="s">
+        <v>156</v>
       </c>
       <c r="E9" s="63"/>
       <c r="F9" s="63"/>
       <c r="G9" s="63"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
-      <c r="J9" s="89"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="102"/>
-      <c r="B10" s="86" t="s">
+      <c r="A10" s="96"/>
+      <c r="B10" s="98" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="64"/>
-      <c r="D10" s="108" t="s">
-        <v>127</v>
+      <c r="D10" s="79" t="s">
+        <v>192</v>
       </c>
       <c r="E10" s="63"/>
       <c r="F10" s="63"/>
       <c r="G10" s="63"/>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
-      <c r="J10" s="89"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="103"/>
-      <c r="B11" s="86" t="s">
+      <c r="A11" s="97"/>
+      <c r="B11" s="98" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="64"/>
       <c r="D11" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="110"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="81"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="94" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="77" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="63"/>
@@ -4559,23 +4860,23 @@
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
-      <c r="J12" s="89"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="91"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="104" t="s">
+      <c r="B13" s="72"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="105"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5566,6 +5867,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5574,25 +5894,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5614,16 +5915,16 @@
       <c r="A1" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5635,46 +5936,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45706</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7025,16 +7326,16 @@
       <c r="A1" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7046,46 +7347,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
         <v>45707</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="83"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8448,16 +8749,16 @@
       <c r="A1" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8469,65 +8770,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
+        <v>45706</v>
+      </c>
+      <c r="I2" s="99" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="102"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="87"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="87"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="103"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="119" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="79">
-        <v>45706</v>
-      </c>
-      <c r="I2" s="82" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="83"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="96"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="84"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="112" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="116" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="114" t="s">
+      <c r="A6" s="112" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="63"/>
@@ -8538,22 +8839,22 @@
       <c r="G6" s="63"/>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
-      <c r="J6" s="89"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="122"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="96"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="66"/>
       <c r="C8" s="66"/>
       <c r="D8" s="66"/>
@@ -8562,10 +8863,10 @@
       <c r="G8" s="66"/>
       <c r="H8" s="66"/>
       <c r="I8" s="66"/>
-      <c r="J8" s="120"/>
+      <c r="J8" s="125"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="96"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
       <c r="D9" s="66"/>
@@ -8574,10 +8875,10 @@
       <c r="G9" s="66"/>
       <c r="H9" s="66"/>
       <c r="I9" s="66"/>
-      <c r="J9" s="120"/>
+      <c r="J9" s="125"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="96"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
       <c r="D10" s="66"/>
@@ -8586,10 +8887,10 @@
       <c r="G10" s="66"/>
       <c r="H10" s="66"/>
       <c r="I10" s="66"/>
-      <c r="J10" s="120"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="96"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
       <c r="D11" s="66"/>
@@ -8598,10 +8899,10 @@
       <c r="G11" s="66"/>
       <c r="H11" s="66"/>
       <c r="I11" s="66"/>
-      <c r="J11" s="120"/>
+      <c r="J11" s="125"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="96"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
       <c r="D12" s="66"/>
@@ -8610,10 +8911,10 @@
       <c r="G12" s="66"/>
       <c r="H12" s="66"/>
       <c r="I12" s="66"/>
-      <c r="J12" s="120"/>
+      <c r="J12" s="125"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="96"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -8622,44 +8923,44 @@
       <c r="G13" s="66"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
-      <c r="J13" s="120"/>
+      <c r="J13" s="125"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="114" t="s">
+      <c r="A14" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="121"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="122"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="121"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="88" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="125"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="116"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="114" t="s">
+      <c r="A16" s="112" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="63"/>
@@ -8680,11 +8981,11 @@
         <v>18</v>
       </c>
       <c r="I16" s="63"/>
-      <c r="J16" s="89"/>
+      <c r="J16" s="78"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="115" t="s">
-        <v>145</v>
+      <c r="A17" s="118" t="s">
+        <v>144</v>
       </c>
       <c r="B17" s="63"/>
       <c r="C17" s="64"/>
@@ -8692,57 +8993,57 @@
         <v>72</v>
       </c>
       <c r="E17" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="H17" s="88" t="s">
-        <v>152</v>
+      <c r="H17" s="77" t="s">
+        <v>151</v>
       </c>
       <c r="I17" s="63"/>
-      <c r="J17" s="89"/>
+      <c r="J17" s="78"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="114" t="s">
+      <c r="A18" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="122"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="114" t="s">
+      <c r="A19" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="121"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="88" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="124"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="125"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="77" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="116"/>
       <c r="I19" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="115" t="s">
-        <v>149</v>
+      <c r="A20" s="118" t="s">
+        <v>148</v>
       </c>
       <c r="B20" s="63"/>
       <c r="C20" s="64"/>
@@ -8750,55 +9051,55 @@
         <v>72</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F20" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="G20" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="G20" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" s="88" t="s">
-        <v>156</v>
+      <c r="H20" s="77" t="s">
+        <v>155</v>
       </c>
       <c r="I20" s="63"/>
-      <c r="J20" s="89"/>
+      <c r="J20" s="78"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="115"/>
+      <c r="A21" s="118"/>
       <c r="B21" s="63"/>
       <c r="C21" s="64"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="88"/>
+      <c r="H21" s="77"/>
       <c r="I21" s="63"/>
-      <c r="J21" s="89"/>
+      <c r="J21" s="78"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="115"/>
+      <c r="A22" s="118"/>
       <c r="B22" s="63"/>
       <c r="C22" s="64"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="88"/>
+      <c r="H22" s="77"/>
       <c r="I22" s="63"/>
-      <c r="J22" s="89"/>
+      <c r="J22" s="78"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="113"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="120"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="105"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="73"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9779,15 +10080,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9804,11 +10101,15 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9864,7 +10165,7 @@
         <v>84</v>
       </c>
       <c r="D3" s="61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1">
@@ -9917,6 +10218,1373 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F65D3F0-BA2A-4190-834F-9E36F90A1EAB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.08984375" customWidth="1"/>
+    <col min="4" max="6" width="16.7265625" customWidth="1"/>
+    <col min="7" max="7" width="20.90625" customWidth="1"/>
+    <col min="8" max="10" width="16.7265625" customWidth="1"/>
+    <col min="11" max="26" width="8.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="111" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="105" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="93"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="87"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="106" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="107"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="99" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="102"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="87"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="87"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="103"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="119" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="121" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="76"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="112" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="78"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="122"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="124"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="87"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="125"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="87"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="125"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="87"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="125"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="87"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="125"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="87"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="125"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="87"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="125"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="112" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="114"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="113"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="63"/>
+      <c r="J16" s="78"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="118" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="147"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="H17" s="77" t="s">
+        <v>196</v>
+      </c>
+      <c r="I17" s="115"/>
+      <c r="J17" s="146"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="118"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="78"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="118"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="78"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="118"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="78"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="118"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="78"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="118"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="78"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="120"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="73"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
@@ -9927,133 +11595,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="71" t="s">
+      <c r="A1" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="71" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="71" t="s">
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="71" t="s">
+      <c r="P1" s="93"/>
+      <c r="Q1" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="72"/>
-      <c r="S1" s="71" t="s">
+      <c r="R1" s="93"/>
+      <c r="S1" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="107"/>
+      <c r="T1" s="76"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
       <c r="D2" s="66"/>
       <c r="E2" s="66"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="119"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="124"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="96"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="66"/>
       <c r="C3" s="66"/>
       <c r="D3" s="66"/>
       <c r="E3" s="66"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="75"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="108"/>
       <c r="H3" s="66"/>
       <c r="I3" s="66"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="75"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="108"/>
       <c r="L3" s="66"/>
       <c r="M3" s="66"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="120"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="125"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="133"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="109"/>
+      <c r="R4" s="91"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="137"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="119" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="106" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="107"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="76"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="114" t="s">
+      <c r="A6" s="112" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="63"/>
@@ -10061,7 +11729,7 @@
       <c r="D6" s="63"/>
       <c r="E6" s="63"/>
       <c r="F6" s="64"/>
-      <c r="G6" s="88" t="s">
+      <c r="G6" s="77" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="63"/>
@@ -10076,10 +11744,10 @@
       <c r="Q6" s="63"/>
       <c r="R6" s="63"/>
       <c r="S6" s="63"/>
-      <c r="T6" s="89"/>
+      <c r="T6" s="78"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="114" t="s">
+      <c r="A7" s="112" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="63"/>
@@ -10087,7 +11755,7 @@
       <c r="D7" s="63"/>
       <c r="E7" s="63"/>
       <c r="F7" s="64"/>
-      <c r="G7" s="88" t="s">
+      <c r="G7" s="77" t="s">
         <v>36</v>
       </c>
       <c r="H7" s="63"/>
@@ -10102,7 +11770,7 @@
       <c r="Q7" s="63"/>
       <c r="R7" s="63"/>
       <c r="S7" s="63"/>
-      <c r="T7" s="89"/>
+      <c r="T7" s="78"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10301,7 +11969,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="112" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="64"/>
@@ -10343,33 +12011,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="134">
+      <c r="A16" s="129">
         <v>1</v>
       </c>
       <c r="B16" s="64"/>
-      <c r="C16" s="135" t="s">
+      <c r="C16" s="130" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="64"/>
-      <c r="E16" s="135" t="s">
+      <c r="E16" s="130" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="64"/>
-      <c r="G16" s="129" t="s">
+      <c r="G16" s="135" t="s">
         <v>54</v>
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="64"/>
-      <c r="J16" s="129" t="s">
+      <c r="J16" s="135" t="s">
         <v>55</v>
       </c>
       <c r="K16" s="64"/>
-      <c r="L16" s="131" t="s">
+      <c r="L16" s="133" t="s">
         <v>56</v>
       </c>
       <c r="M16" s="63"/>
       <c r="N16" s="64"/>
-      <c r="O16" s="131" t="s">
+      <c r="O16" s="133" t="s">
         <v>57</v>
       </c>
       <c r="P16" s="63"/>
@@ -10385,33 +12053,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="134">
+      <c r="A17" s="129">
         <v>2</v>
       </c>
       <c r="B17" s="64"/>
-      <c r="C17" s="135" t="s">
+      <c r="C17" s="130" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="64"/>
-      <c r="E17" s="135" t="s">
+      <c r="E17" s="130" t="s">
         <v>59</v>
       </c>
       <c r="F17" s="64"/>
-      <c r="G17" s="129" t="s">
+      <c r="G17" s="135" t="s">
         <v>60</v>
       </c>
       <c r="H17" s="63"/>
       <c r="I17" s="64"/>
-      <c r="J17" s="129" t="s">
+      <c r="J17" s="135" t="s">
         <v>61</v>
       </c>
       <c r="K17" s="64"/>
-      <c r="L17" s="131" t="s">
+      <c r="L17" s="133" t="s">
         <v>62</v>
       </c>
       <c r="M17" s="63"/>
       <c r="N17" s="64"/>
-      <c r="O17" s="131" t="s">
+      <c r="O17" s="133" t="s">
         <v>63</v>
       </c>
       <c r="P17" s="63"/>
@@ -10427,21 +12095,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="134"/>
+      <c r="A18" s="129"/>
       <c r="B18" s="64"/>
-      <c r="C18" s="135"/>
+      <c r="C18" s="130"/>
       <c r="D18" s="64"/>
-      <c r="E18" s="135"/>
+      <c r="E18" s="130"/>
       <c r="F18" s="64"/>
-      <c r="G18" s="129"/>
+      <c r="G18" s="135"/>
       <c r="H18" s="63"/>
       <c r="I18" s="64"/>
-      <c r="J18" s="129"/>
+      <c r="J18" s="135"/>
       <c r="K18" s="64"/>
-      <c r="L18" s="131"/>
+      <c r="L18" s="133"/>
       <c r="M18" s="63"/>
       <c r="N18" s="64"/>
-      <c r="O18" s="131"/>
+      <c r="O18" s="133"/>
       <c r="P18" s="63"/>
       <c r="Q18" s="64"/>
       <c r="R18" s="33"/>
@@ -10455,21 +12123,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="134"/>
+      <c r="A19" s="129"/>
       <c r="B19" s="64"/>
-      <c r="C19" s="135"/>
+      <c r="C19" s="130"/>
       <c r="D19" s="64"/>
-      <c r="E19" s="135"/>
+      <c r="E19" s="130"/>
       <c r="F19" s="64"/>
-      <c r="G19" s="129"/>
+      <c r="G19" s="135"/>
       <c r="H19" s="63"/>
       <c r="I19" s="64"/>
-      <c r="J19" s="129"/>
+      <c r="J19" s="135"/>
       <c r="K19" s="64"/>
-      <c r="L19" s="131"/>
+      <c r="L19" s="133"/>
       <c r="M19" s="63"/>
       <c r="N19" s="64"/>
-      <c r="O19" s="131"/>
+      <c r="O19" s="133"/>
       <c r="P19" s="63"/>
       <c r="Q19" s="64"/>
       <c r="R19" s="33"/>
@@ -10483,21 +12151,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="134"/>
+      <c r="A20" s="129"/>
       <c r="B20" s="64"/>
-      <c r="C20" s="135"/>
+      <c r="C20" s="130"/>
       <c r="D20" s="64"/>
-      <c r="E20" s="135"/>
+      <c r="E20" s="130"/>
       <c r="F20" s="64"/>
-      <c r="G20" s="129"/>
+      <c r="G20" s="135"/>
       <c r="H20" s="63"/>
       <c r="I20" s="64"/>
-      <c r="J20" s="129"/>
+      <c r="J20" s="135"/>
       <c r="K20" s="64"/>
-      <c r="L20" s="131"/>
+      <c r="L20" s="133"/>
       <c r="M20" s="63"/>
       <c r="N20" s="64"/>
-      <c r="O20" s="131"/>
+      <c r="O20" s="133"/>
       <c r="P20" s="63"/>
       <c r="Q20" s="64"/>
       <c r="R20" s="33"/>
@@ -10511,21 +12179,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="134"/>
+      <c r="A21" s="129"/>
       <c r="B21" s="64"/>
-      <c r="C21" s="135"/>
+      <c r="C21" s="130"/>
       <c r="D21" s="64"/>
-      <c r="E21" s="135"/>
+      <c r="E21" s="130"/>
       <c r="F21" s="64"/>
-      <c r="G21" s="129"/>
+      <c r="G21" s="135"/>
       <c r="H21" s="63"/>
       <c r="I21" s="64"/>
-      <c r="J21" s="129"/>
+      <c r="J21" s="135"/>
       <c r="K21" s="64"/>
-      <c r="L21" s="131"/>
+      <c r="L21" s="133"/>
       <c r="M21" s="63"/>
       <c r="N21" s="64"/>
-      <c r="O21" s="131"/>
+      <c r="O21" s="133"/>
       <c r="P21" s="63"/>
       <c r="Q21" s="64"/>
       <c r="R21" s="33"/>
@@ -10539,21 +12207,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="134"/>
+      <c r="A22" s="129"/>
       <c r="B22" s="64"/>
-      <c r="C22" s="135"/>
+      <c r="C22" s="130"/>
       <c r="D22" s="64"/>
-      <c r="E22" s="135"/>
+      <c r="E22" s="130"/>
       <c r="F22" s="64"/>
-      <c r="G22" s="129"/>
+      <c r="G22" s="135"/>
       <c r="H22" s="63"/>
       <c r="I22" s="64"/>
-      <c r="J22" s="129"/>
+      <c r="J22" s="135"/>
       <c r="K22" s="64"/>
-      <c r="L22" s="131"/>
+      <c r="L22" s="133"/>
       <c r="M22" s="63"/>
       <c r="N22" s="64"/>
-      <c r="O22" s="131"/>
+      <c r="O22" s="133"/>
       <c r="P22" s="63"/>
       <c r="Q22" s="64"/>
       <c r="R22" s="33"/>
@@ -10567,21 +12235,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="134"/>
+      <c r="A23" s="129"/>
       <c r="B23" s="64"/>
-      <c r="C23" s="135"/>
+      <c r="C23" s="130"/>
       <c r="D23" s="64"/>
-      <c r="E23" s="135"/>
+      <c r="E23" s="130"/>
       <c r="F23" s="64"/>
-      <c r="G23" s="129"/>
+      <c r="G23" s="135"/>
       <c r="H23" s="63"/>
       <c r="I23" s="64"/>
-      <c r="J23" s="129"/>
+      <c r="J23" s="135"/>
       <c r="K23" s="64"/>
-      <c r="L23" s="131"/>
+      <c r="L23" s="133"/>
       <c r="M23" s="63"/>
       <c r="N23" s="64"/>
-      <c r="O23" s="131"/>
+      <c r="O23" s="133"/>
       <c r="P23" s="63"/>
       <c r="Q23" s="64"/>
       <c r="R23" s="33"/>
@@ -10595,21 +12263,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="134"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="64"/>
-      <c r="C24" s="135"/>
+      <c r="C24" s="130"/>
       <c r="D24" s="64"/>
-      <c r="E24" s="135"/>
+      <c r="E24" s="130"/>
       <c r="F24" s="64"/>
-      <c r="G24" s="129"/>
+      <c r="G24" s="135"/>
       <c r="H24" s="63"/>
       <c r="I24" s="64"/>
-      <c r="J24" s="129"/>
+      <c r="J24" s="135"/>
       <c r="K24" s="64"/>
-      <c r="L24" s="131"/>
+      <c r="L24" s="133"/>
       <c r="M24" s="63"/>
       <c r="N24" s="64"/>
-      <c r="O24" s="131"/>
+      <c r="O24" s="133"/>
       <c r="P24" s="63"/>
       <c r="Q24" s="64"/>
       <c r="R24" s="33"/>
@@ -10623,21 +12291,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="134"/>
+      <c r="A25" s="129"/>
       <c r="B25" s="64"/>
-      <c r="C25" s="135"/>
+      <c r="C25" s="130"/>
       <c r="D25" s="64"/>
-      <c r="E25" s="135"/>
+      <c r="E25" s="130"/>
       <c r="F25" s="64"/>
-      <c r="G25" s="129"/>
+      <c r="G25" s="135"/>
       <c r="H25" s="63"/>
       <c r="I25" s="64"/>
-      <c r="J25" s="129"/>
+      <c r="J25" s="135"/>
       <c r="K25" s="64"/>
-      <c r="L25" s="131"/>
+      <c r="L25" s="133"/>
       <c r="M25" s="63"/>
       <c r="N25" s="64"/>
-      <c r="O25" s="131"/>
+      <c r="O25" s="133"/>
       <c r="P25" s="63"/>
       <c r="Q25" s="64"/>
       <c r="R25" s="33"/>
@@ -10651,21 +12319,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="134"/>
+      <c r="A26" s="129"/>
       <c r="B26" s="64"/>
-      <c r="C26" s="135"/>
+      <c r="C26" s="130"/>
       <c r="D26" s="64"/>
-      <c r="E26" s="135"/>
+      <c r="E26" s="130"/>
       <c r="F26" s="64"/>
-      <c r="G26" s="129"/>
+      <c r="G26" s="135"/>
       <c r="H26" s="63"/>
       <c r="I26" s="64"/>
-      <c r="J26" s="129"/>
+      <c r="J26" s="135"/>
       <c r="K26" s="64"/>
-      <c r="L26" s="131"/>
+      <c r="L26" s="133"/>
       <c r="M26" s="63"/>
       <c r="N26" s="64"/>
-      <c r="O26" s="131"/>
+      <c r="O26" s="133"/>
       <c r="P26" s="63"/>
       <c r="Q26" s="64"/>
       <c r="R26" s="33"/>
@@ -10679,21 +12347,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="134"/>
+      <c r="A27" s="129"/>
       <c r="B27" s="64"/>
-      <c r="C27" s="135"/>
+      <c r="C27" s="130"/>
       <c r="D27" s="64"/>
-      <c r="E27" s="135"/>
+      <c r="E27" s="130"/>
       <c r="F27" s="64"/>
-      <c r="G27" s="129"/>
+      <c r="G27" s="135"/>
       <c r="H27" s="63"/>
       <c r="I27" s="64"/>
-      <c r="J27" s="129"/>
+      <c r="J27" s="135"/>
       <c r="K27" s="64"/>
-      <c r="L27" s="131"/>
+      <c r="L27" s="133"/>
       <c r="M27" s="63"/>
       <c r="N27" s="64"/>
-      <c r="O27" s="131"/>
+      <c r="O27" s="133"/>
       <c r="P27" s="63"/>
       <c r="Q27" s="64"/>
       <c r="R27" s="33"/>
@@ -10707,21 +12375,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="134"/>
+      <c r="A28" s="129"/>
       <c r="B28" s="64"/>
-      <c r="C28" s="135"/>
+      <c r="C28" s="130"/>
       <c r="D28" s="64"/>
-      <c r="E28" s="135"/>
+      <c r="E28" s="130"/>
       <c r="F28" s="64"/>
-      <c r="G28" s="129"/>
+      <c r="G28" s="135"/>
       <c r="H28" s="63"/>
       <c r="I28" s="64"/>
-      <c r="J28" s="129"/>
+      <c r="J28" s="135"/>
       <c r="K28" s="64"/>
-      <c r="L28" s="131"/>
+      <c r="L28" s="133"/>
       <c r="M28" s="63"/>
       <c r="N28" s="64"/>
-      <c r="O28" s="131"/>
+      <c r="O28" s="133"/>
       <c r="P28" s="63"/>
       <c r="Q28" s="64"/>
       <c r="R28" s="33"/>
@@ -10735,21 +12403,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="134"/>
+      <c r="A29" s="129"/>
       <c r="B29" s="64"/>
-      <c r="C29" s="135"/>
+      <c r="C29" s="130"/>
       <c r="D29" s="64"/>
-      <c r="E29" s="135"/>
+      <c r="E29" s="130"/>
       <c r="F29" s="64"/>
-      <c r="G29" s="129"/>
+      <c r="G29" s="135"/>
       <c r="H29" s="63"/>
       <c r="I29" s="64"/>
-      <c r="J29" s="129"/>
+      <c r="J29" s="135"/>
       <c r="K29" s="64"/>
-      <c r="L29" s="131"/>
+      <c r="L29" s="133"/>
       <c r="M29" s="63"/>
       <c r="N29" s="64"/>
-      <c r="O29" s="131"/>
+      <c r="O29" s="133"/>
       <c r="P29" s="63"/>
       <c r="Q29" s="64"/>
       <c r="R29" s="33"/>
@@ -10763,21 +12431,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="134"/>
+      <c r="A30" s="129"/>
       <c r="B30" s="64"/>
-      <c r="C30" s="135"/>
+      <c r="C30" s="130"/>
       <c r="D30" s="64"/>
-      <c r="E30" s="135"/>
+      <c r="E30" s="130"/>
       <c r="F30" s="64"/>
-      <c r="G30" s="129"/>
+      <c r="G30" s="135"/>
       <c r="H30" s="63"/>
       <c r="I30" s="64"/>
-      <c r="J30" s="129"/>
+      <c r="J30" s="135"/>
       <c r="K30" s="64"/>
-      <c r="L30" s="131"/>
+      <c r="L30" s="133"/>
       <c r="M30" s="63"/>
       <c r="N30" s="64"/>
-      <c r="O30" s="131"/>
+      <c r="O30" s="133"/>
       <c r="P30" s="63"/>
       <c r="Q30" s="64"/>
       <c r="R30" s="33"/>
@@ -10791,23 +12459,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="130"/>
-      <c r="K31" s="92"/>
-      <c r="L31" s="132"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="132"/>
-      <c r="P31" s="91"/>
-      <c r="Q31" s="92"/>
+      <c r="A31" s="131"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="132"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="83"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="83"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11805,6 +13473,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11829,118 +13609,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11948,7 +13616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5CECE2-1A29-4C94-94D4-07CF7FB29E2C}">
   <dimension ref="B1:L59"/>
   <sheetFormatPr defaultRowHeight="13" customHeight="1"/>
@@ -11966,45 +13634,45 @@
     <row r="1" spans="6:12" ht="13" customHeight="1" thickBot="1"/>
     <row r="2" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="F2" s="143" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H2" s="54"/>
       <c r="I2" s="55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="F3" s="144"/>
       <c r="H3" s="56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I3" s="57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="F4" s="145"/>
       <c r="H4" s="58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I4" s="59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="H5" s="58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="6:12" ht="13" customHeight="1" thickBot="1">
       <c r="H6" s="56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I6" s="57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="6:12" ht="13" customHeight="1" thickBot="1"/>
@@ -12014,7 +13682,7 @@
       </c>
       <c r="I8" s="140"/>
       <c r="L8" s="39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="6:12" ht="13" customHeight="1">
@@ -12028,7 +13696,7 @@
         <v>72</v>
       </c>
       <c r="L9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="6:12" ht="13" customHeight="1">
@@ -12042,7 +13710,7 @@
         <v>72</v>
       </c>
       <c r="L10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="6:12" ht="13" customHeight="1">
@@ -12056,7 +13724,7 @@
         <v>72</v>
       </c>
       <c r="L11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="6:12" ht="13" customHeight="1">
@@ -12070,7 +13738,7 @@
         <v>72</v>
       </c>
       <c r="L12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="6:12" ht="13" customHeight="1">
@@ -12084,7 +13752,7 @@
         <v>72</v>
       </c>
       <c r="L13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="6:12" ht="13" customHeight="1">
@@ -12098,7 +13766,7 @@
         <v>72</v>
       </c>
       <c r="L14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="6:12" ht="13" customHeight="1">
@@ -12112,7 +13780,7 @@
         <v>72</v>
       </c>
       <c r="L15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="6:12" ht="13" customHeight="1">
@@ -12126,7 +13794,7 @@
         <v>72</v>
       </c>
       <c r="L16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="8:12" ht="13" customHeight="1">
@@ -12140,7 +13808,7 @@
         <v>72</v>
       </c>
       <c r="L17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="8:12" ht="13" customHeight="1">
@@ -12154,7 +13822,7 @@
         <v>72</v>
       </c>
       <c r="L18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="8:12" ht="13" customHeight="1">
@@ -12168,7 +13836,7 @@
         <v>72</v>
       </c>
       <c r="L19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="8:12" ht="13" customHeight="1">
@@ -12182,7 +13850,7 @@
         <v>72</v>
       </c>
       <c r="L20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="8:12" ht="13" customHeight="1">
@@ -12196,7 +13864,7 @@
         <v>72</v>
       </c>
       <c r="L21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="8:12" ht="13" customHeight="1">
@@ -12210,7 +13878,7 @@
         <v>105</v>
       </c>
       <c r="L22" s="39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="8:12" ht="13" customHeight="1">
@@ -12252,7 +13920,7 @@
         <v>105</v>
       </c>
       <c r="L25" s="39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="8:12" ht="13" customHeight="1">
@@ -12266,7 +13934,7 @@
         <v>105</v>
       </c>
       <c r="L26" s="39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="8:12" ht="13" customHeight="1">
@@ -12280,7 +13948,7 @@
         <v>105</v>
       </c>
       <c r="L27" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="8:12" ht="13" customHeight="1">
@@ -12294,7 +13962,7 @@
         <v>105</v>
       </c>
       <c r="L28" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="8:12" ht="13" customHeight="1">
@@ -12308,7 +13976,7 @@
         <v>105</v>
       </c>
       <c r="L29" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="8:12" ht="13" customHeight="1">
@@ -12322,7 +13990,7 @@
         <v>105</v>
       </c>
       <c r="L30" s="39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="8:12" ht="13" customHeight="1">
@@ -12336,7 +14004,7 @@
         <v>105</v>
       </c>
       <c r="L31" s="39" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="8:12" ht="13" customHeight="1">
@@ -12350,7 +14018,7 @@
         <v>105</v>
       </c>
       <c r="L32" s="39" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="13" customHeight="1">
@@ -12378,7 +14046,7 @@
         <v>105</v>
       </c>
       <c r="L34" s="39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="13" customHeight="1">
@@ -12392,7 +14060,7 @@
         <v>105</v>
       </c>
       <c r="L35" s="39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="13" customHeight="1" thickBot="1">
@@ -12406,7 +14074,7 @@
         <v>105</v>
       </c>
       <c r="L36" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="13" customHeight="1" thickBot="1">
@@ -12419,22 +14087,22 @@
     </row>
     <row r="38" spans="2:12" ht="13" customHeight="1" thickBot="1">
       <c r="H38" s="141" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I38" s="142"/>
       <c r="K38" s="39" t="s">
         <v>105</v>
       </c>
       <c r="L38" s="39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="13" customHeight="1" thickBot="1">
       <c r="H39" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="I39" s="49" t="s">
         <v>129</v>
-      </c>
-      <c r="I39" s="49" t="s">
-        <v>130</v>
       </c>
       <c r="K39" s="39" t="s">
         <v>105</v>
@@ -12445,10 +14113,10 @@
     </row>
     <row r="40" spans="2:12" ht="13" customHeight="1" thickBot="1">
       <c r="H40" s="48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I40" s="49" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K40" s="39" t="s">
         <v>105</v>
@@ -12459,10 +14127,10 @@
     </row>
     <row r="41" spans="2:12" ht="13" customHeight="1" thickBot="1">
       <c r="H41" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K41" s="39" t="s">
         <v>105</v>
@@ -12473,10 +14141,10 @@
     </row>
     <row r="42" spans="2:12" ht="13" customHeight="1" thickBot="1">
       <c r="H42" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="I42" s="51" t="s">
         <v>133</v>
-      </c>
-      <c r="I42" s="51" t="s">
-        <v>134</v>
       </c>
       <c r="K42" s="39" t="s">
         <v>105</v>
@@ -12523,13 +14191,13 @@
         <v>126</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K46" s="39" t="s">
         <v>105</v>
       </c>
       <c r="L46" s="39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="2:12" ht="13" customHeight="1" thickBot="1">
@@ -12537,13 +14205,13 @@
         <v>105</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H47" s="39" t="s">
         <v>72</v>
       </c>
       <c r="I47" s="39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K47" s="39" t="s">
         <v>105</v>
@@ -12557,13 +14225,13 @@
         <v>72</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K48" s="39" t="s">
         <v>105</v>
       </c>
       <c r="L48" s="39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="8:9" ht="13" customHeight="1">
@@ -12571,7 +14239,7 @@
         <v>72</v>
       </c>
       <c r="I49" s="39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="8:9" ht="13" customHeight="1">
@@ -12587,7 +14255,7 @@
         <v>105</v>
       </c>
       <c r="I51" s="39" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="8:9" ht="13" customHeight="1">
@@ -12611,7 +14279,7 @@
         <v>105</v>
       </c>
       <c r="I54" s="38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="8:9" ht="13" customHeight="1">
@@ -12619,7 +14287,7 @@
         <v>105</v>
       </c>
       <c r="I55" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="8:9" ht="13" customHeight="1">
@@ -12627,7 +14295,7 @@
         <v>105</v>
       </c>
       <c r="I56" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="8:9" ht="13" customHeight="1">
@@ -12635,7 +14303,7 @@
         <v>105</v>
       </c>
       <c r="I57" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="8:9" ht="13" customHeight="1">
